--- a/Datos.xlsx
+++ b/Datos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WorkSpace\preenfrio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chanitosfrutas-my.sharepoint.com/personal/bescobedo_chanitos_com/Documents/WorkSpace/preenfrio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A36C04-E6E5-4B51-9906-23526A19135B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{F0A36C04-E6E5-4B51-9906-23526A19135B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D71ADB7D-78C4-4237-98B4-D9484E993E1F}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{870F0A8F-B5CF-4FD7-9FD6-C646EB212759}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{870F0A8F-B5CF-4FD7-9FD6-C646EB212759}"/>
   </bookViews>
   <sheets>
     <sheet name="PREENFRIO" sheetId="1" r:id="rId1"/>
@@ -18,10 +18,12 @@
     <sheet name="RANGOS TEMPERATURA" sheetId="5" r:id="rId3"/>
     <sheet name="FINCAS" sheetId="3" r:id="rId4"/>
     <sheet name="SKU" sheetId="4" r:id="rId5"/>
+    <sheet name="PRODUCTORES" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLIENTES-CEDIS'!$A$1:$C$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">FINCAS!$A$1:$B$284</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">PRODUCTORES!$A$1:$C$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RANGOS TEMPERATURA'!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">SKU!$A$1:$B$39</definedName>
   </definedNames>
@@ -49,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="793">
   <si>
     <t>PREENFRIO</t>
   </si>
@@ -2011,6 +2013,423 @@
   </si>
   <si>
     <t>B20 228 Zaragoza 2</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>('CDS06124','Chanitos Snack'),</t>
+  </si>
+  <si>
+    <t>('CCL02114','Chanitos Classic Granel'),</t>
+  </si>
+  <si>
+    <t>('CDM10137','Chanitos Dominico 1ra'),</t>
+  </si>
+  <si>
+    <t>('CDM10138','Chanitos Dominico 2da'),</t>
+  </si>
+  <si>
+    <t>('CDS04122','Chanitos Cha Cha Cha (DS) Granel'),</t>
+  </si>
+  <si>
+    <t>('CDS04123','Chanitos Premium Granel'),</t>
+  </si>
+  <si>
+    <t>('CDS04125','Chanitos Premium Tarima Chep'),</t>
+  </si>
+  <si>
+    <t>('CMN05123','Chanitos Manitas Granel'),</t>
+  </si>
+  <si>
+    <t>('CPL08133','Chanitos Plantain 50lb Tarima Americana'),</t>
+  </si>
+  <si>
+    <t>('CPL08134','Chanitos Plantain 20Kg Tarima Americana'),</t>
+  </si>
+  <si>
+    <t>('CPL08141','Chanitos Plantain 20Kg Tarima Chep'),</t>
+  </si>
+  <si>
+    <t>('CPR01101','Chanitos Premium Granel'),</t>
+  </si>
+  <si>
+    <t>('CPR01102','Chanitos Premium Tarima Chep'),</t>
+  </si>
+  <si>
+    <t>('CPR01103','Chanitos Premium Tarima Americana'),</t>
+  </si>
+  <si>
+    <t>('CPR01104','Chanitos Premium EUA Tarima Americana'),</t>
+  </si>
+  <si>
+    <t>('CPR01106','Chanitos Premium 22XU CP34 Union'),</t>
+  </si>
+  <si>
+    <t>('CPR01107','Chanitos Premium 22XU CP30 Union'),</t>
+  </si>
+  <si>
+    <t>('CPR01108','Chanitos Premium 22XU CP26 Union'),</t>
+  </si>
+  <si>
+    <t>('CPR01109','Chanitos Premium 22XU CP26 WR'),</t>
+  </si>
+  <si>
+    <t>('CPR01111','Chanitos Premium 22XU CP28 Royal'),</t>
+  </si>
+  <si>
+    <t>('CPR01112','Chanitos Premium 22XU CL25 Royal'),</t>
+  </si>
+  <si>
+    <t>('CPR01113','Chanitos Premium 22XU CL13 Royal'),</t>
+  </si>
+  <si>
+    <t>('CPR01114','Platano de Chiapas BAE UPC 3237'),</t>
+  </si>
+  <si>
+    <t>('CPR01115','Chanitos Premium 22XU CP28 Royal'),</t>
+  </si>
+  <si>
+    <t>('CPR01116','Chanitos Premium 22XU CP26 Royal'),</t>
+  </si>
+  <si>
+    <t>('CPR03117','Chanitos Cha Cha Cha 22XU CP26 Mar Kodawari'),</t>
+  </si>
+  <si>
+    <t>('CPR03119','Chanitos Cha Cha Cha 22XU  CP34 Mar Kodawari'),</t>
+  </si>
+  <si>
+    <t>('CPR03123','Chanitos Premium Tarima Chep Banda 3b'),</t>
+  </si>
+  <si>
+    <t>('CPR03124','Chanitos Cha Cha Cha 22XU CP27 Mar Kodawari'),</t>
+  </si>
+  <si>
+    <t>('CRG07125','Chanitos Organic Banded Tape Verde'),</t>
+  </si>
+  <si>
+    <t>('CRG07127','Chanitos Organic 3lb Banded Tape Morado'),</t>
+  </si>
+  <si>
+    <t>('CRG07128','Chanitos Organic Banded Market Side Mexico'),</t>
+  </si>
+  <si>
+    <t>('CRG07129','Chanitos Organic Banded Market Side EUA'),</t>
+  </si>
+  <si>
+    <t>('CRG07130','Chanitos Organic  22XU CP28 Union'),</t>
+  </si>
+  <si>
+    <t>('CRG07131','Chanitos Organic  22XU CP34 Union'),</t>
+  </si>
+  <si>
+    <t>('CRG07132','Organic  Wild Harvest '),</t>
+  </si>
+  <si>
+    <t>('CRG07133','Chanitos Organic  Wild Harvest PLU94011'),</t>
+  </si>
+  <si>
+    <t>('CSA04120','Chanitos Cha Cha Cha (2da) Granel')</t>
+  </si>
+  <si>
+    <t>Productor</t>
+  </si>
+  <si>
+    <t>A27</t>
+  </si>
+  <si>
+    <t>Salim Rodriguez</t>
+  </si>
+  <si>
+    <t>A01</t>
+  </si>
+  <si>
+    <t>La Santanera</t>
+  </si>
+  <si>
+    <t>A04</t>
+  </si>
+  <si>
+    <t>Rafael Nava</t>
+  </si>
+  <si>
+    <t>A11</t>
+  </si>
+  <si>
+    <t>Sector Mazatan</t>
+  </si>
+  <si>
+    <t>A35</t>
+  </si>
+  <si>
+    <t>Abimael Tovar</t>
+  </si>
+  <si>
+    <t>A05</t>
+  </si>
+  <si>
+    <t>Plataneros Unidos</t>
+  </si>
+  <si>
+    <t>B07</t>
+  </si>
+  <si>
+    <t>Erick Viveros</t>
+  </si>
+  <si>
+    <t>B12</t>
+  </si>
+  <si>
+    <t>Ramon Larios</t>
+  </si>
+  <si>
+    <t>B01</t>
+  </si>
+  <si>
+    <t>Ricamp</t>
+  </si>
+  <si>
+    <t>B05</t>
+  </si>
+  <si>
+    <t>Maria Elena</t>
+  </si>
+  <si>
+    <t>B02</t>
+  </si>
+  <si>
+    <t>Ochoa</t>
+  </si>
+  <si>
+    <t>B14</t>
+  </si>
+  <si>
+    <t>German Gomez</t>
+  </si>
+  <si>
+    <t>B03</t>
+  </si>
+  <si>
+    <t>Larifrut</t>
+  </si>
+  <si>
+    <t>B20</t>
+  </si>
+  <si>
+    <t>Jorge Garcia</t>
+  </si>
+  <si>
+    <t>B06</t>
+  </si>
+  <si>
+    <t>Jose Rivera</t>
+  </si>
+  <si>
+    <t>B15</t>
+  </si>
+  <si>
+    <t>Juan Valdivia</t>
+  </si>
+  <si>
+    <t>B19</t>
+  </si>
+  <si>
+    <t>Dulce Arceo</t>
+  </si>
+  <si>
+    <t>C05</t>
+  </si>
+  <si>
+    <t>Luis Olguin</t>
+  </si>
+  <si>
+    <t>C01</t>
+  </si>
+  <si>
+    <t>Finca Genesis</t>
+  </si>
+  <si>
+    <t>C18</t>
+  </si>
+  <si>
+    <t>Felipe de Jesus Cervantes Ledezma</t>
+  </si>
+  <si>
+    <t>C19</t>
+  </si>
+  <si>
+    <t>Felipe Martinez Ruiz</t>
+  </si>
+  <si>
+    <t>A36</t>
+  </si>
+  <si>
+    <t>Herbert Blanco</t>
+  </si>
+  <si>
+    <t>E06</t>
+  </si>
+  <si>
+    <t>Leonter Martinez Gonzalez</t>
+  </si>
+  <si>
+    <t>A26</t>
+  </si>
+  <si>
+    <t>Manuel Tamayo</t>
+  </si>
+  <si>
+    <t>A25</t>
+  </si>
+  <si>
+    <t>Gerardo Turriza</t>
+  </si>
+  <si>
+    <t>C11</t>
+  </si>
+  <si>
+    <t>Javier Moreno</t>
+  </si>
+  <si>
+    <t>B04</t>
+  </si>
+  <si>
+    <t>Banamac</t>
+  </si>
+  <si>
+    <t>A38</t>
+  </si>
+  <si>
+    <t>Exal Moreno</t>
+  </si>
+  <si>
+    <t>A39</t>
+  </si>
+  <si>
+    <t>Nallely Gonzalez</t>
+  </si>
+  <si>
+    <t>B21</t>
+  </si>
+  <si>
+    <t>Aldo Rincon</t>
+  </si>
+  <si>
+    <t>Nayeli Gonzalez</t>
+  </si>
+  <si>
+    <t>B22</t>
+  </si>
+  <si>
+    <t>Celeste Moreno</t>
+  </si>
+  <si>
+    <t>B23</t>
+  </si>
+  <si>
+    <t>Fabiola Moreno</t>
+  </si>
+  <si>
+    <t>A40</t>
+  </si>
+  <si>
+    <t>Secundino Beitia</t>
+  </si>
+  <si>
+    <t>A06</t>
+  </si>
+  <si>
+    <t>Antelmo Sandoval</t>
+  </si>
+  <si>
+    <t>B24</t>
+  </si>
+  <si>
+    <t>Jorge Ochoa</t>
+  </si>
+  <si>
+    <t>C09</t>
+  </si>
+  <si>
+    <t>Josefa Gonzales</t>
+  </si>
+  <si>
+    <t>C20</t>
+  </si>
+  <si>
+    <t>Mardonio Morales Luna</t>
+  </si>
+  <si>
+    <t>A08</t>
+  </si>
+  <si>
+    <t>Obdulio Barrios</t>
+  </si>
+  <si>
+    <t>C16</t>
+  </si>
+  <si>
+    <t>Fabiola Pedrero</t>
+  </si>
+  <si>
+    <t>C07</t>
+  </si>
+  <si>
+    <t>Fernando Cano</t>
+  </si>
+  <si>
+    <t>C04</t>
+  </si>
+  <si>
+    <t>Jesus Castro</t>
+  </si>
+  <si>
+    <t>A03</t>
+  </si>
+  <si>
+    <t>Hugo de la Cruz</t>
+  </si>
+  <si>
+    <t>A41</t>
+  </si>
+  <si>
+    <t>Juan Carlos Rebuelta</t>
+  </si>
+  <si>
+    <t>A12</t>
+  </si>
+  <si>
+    <t>Carlos Cigarroa</t>
+  </si>
+  <si>
+    <t>A09</t>
+  </si>
+  <si>
+    <t>Miguel Aleman</t>
+  </si>
+  <si>
+    <t>Jair Velazquez</t>
+  </si>
+  <si>
+    <t>B08</t>
+  </si>
+  <si>
+    <t>Ramon Peña</t>
+  </si>
+  <si>
+    <t>B25</t>
+  </si>
+  <si>
+    <t>David Feliciano</t>
+  </si>
+  <si>
+    <t>Deyvi Feliciano</t>
+  </si>
+  <si>
+    <t>CODIGO</t>
+  </si>
+  <si>
+    <t>ACTIVO</t>
   </si>
 </sst>
 </file>
@@ -2093,7 +2512,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2127,6 +2546,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5655,14 +6083,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{961DD99E-A2C7-4E25-8FB0-84DFB4FA4937}">
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="68.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>574</v>
       </c>
@@ -5670,308 +6098,954 @@
         <v>575</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>648</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E2" t="str">
+        <f>+"'"&amp;A2&amp;"'"</f>
+        <v>'CDS06124'</v>
+      </c>
+      <c r="F2" t="s">
+        <v>654</v>
+      </c>
+      <c r="G2" t="str">
+        <f>+"'"&amp;B2&amp;"'"</f>
+        <v>'Chanitos Snack'</v>
+      </c>
+      <c r="H2" t="s">
+        <v>654</v>
+      </c>
+      <c r="I2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>630</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>631</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E3" t="str">
+        <f t="shared" ref="E3:E39" si="0">+"'"&amp;A3&amp;"'"</f>
+        <v>'CCL02114'</v>
+      </c>
+      <c r="F3" t="s">
+        <v>654</v>
+      </c>
+      <c r="G3" t="str">
+        <f t="shared" ref="G3:G39" si="1">+"'"&amp;B3&amp;"'"</f>
+        <v>'Chanitos Classic Granel'</v>
+      </c>
+      <c r="H3" t="s">
+        <v>654</v>
+      </c>
+      <c r="I3" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>634</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>637</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E4" t="str">
+        <f t="shared" si="0"/>
+        <v>'CDM10137'</v>
+      </c>
+      <c r="F4" t="s">
+        <v>654</v>
+      </c>
+      <c r="G4" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Dominico 1ra'</v>
+      </c>
+      <c r="H4" t="s">
+        <v>654</v>
+      </c>
+      <c r="I4" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>627</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>628</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E5" t="str">
+        <f t="shared" si="0"/>
+        <v>'CDM10138'</v>
+      </c>
+      <c r="F5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G5" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Dominico 2da'</v>
+      </c>
+      <c r="H5" t="s">
+        <v>654</v>
+      </c>
+      <c r="I5" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>591</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E6" t="str">
+        <f t="shared" si="0"/>
+        <v>'CDS04122'</v>
+      </c>
+      <c r="F6" t="s">
+        <v>654</v>
+      </c>
+      <c r="G6" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Cha Cha Cha (DS) Granel'</v>
+      </c>
+      <c r="H6" t="s">
+        <v>654</v>
+      </c>
+      <c r="I6" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>643</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E7" t="str">
+        <f t="shared" si="0"/>
+        <v>'CDS04123'</v>
+      </c>
+      <c r="F7" t="s">
+        <v>654</v>
+      </c>
+      <c r="G7" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Premium Granel'</v>
+      </c>
+      <c r="H7" t="s">
+        <v>654</v>
+      </c>
+      <c r="I7" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>644</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E8" t="str">
+        <f t="shared" si="0"/>
+        <v>'CDS04125'</v>
+      </c>
+      <c r="F8" t="s">
+        <v>654</v>
+      </c>
+      <c r="G8" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Premium Tarima Chep'</v>
+      </c>
+      <c r="H8" t="s">
+        <v>654</v>
+      </c>
+      <c r="I8" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>589</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E9" t="str">
+        <f t="shared" si="0"/>
+        <v>'CMN05123'</v>
+      </c>
+      <c r="F9" t="s">
+        <v>654</v>
+      </c>
+      <c r="G9" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Manitas Granel'</v>
+      </c>
+      <c r="H9" t="s">
+        <v>654</v>
+      </c>
+      <c r="I9" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>576</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E10" t="str">
+        <f t="shared" si="0"/>
+        <v>'CPL08133'</v>
+      </c>
+      <c r="F10" t="s">
+        <v>654</v>
+      </c>
+      <c r="G10" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Plantain 50lb Tarima Americana'</v>
+      </c>
+      <c r="H10" t="s">
+        <v>654</v>
+      </c>
+      <c r="I10" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>599</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E11" t="str">
+        <f t="shared" si="0"/>
+        <v>'CPL08134'</v>
+      </c>
+      <c r="F11" t="s">
+        <v>654</v>
+      </c>
+      <c r="G11" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Plantain 20Kg Tarima Americana'</v>
+      </c>
+      <c r="H11" t="s">
+        <v>654</v>
+      </c>
+      <c r="I11" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>601</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E12" t="str">
+        <f t="shared" si="0"/>
+        <v>'CPL08141'</v>
+      </c>
+      <c r="F12" t="s">
+        <v>654</v>
+      </c>
+      <c r="G12" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Plantain 20Kg Tarima Chep'</v>
+      </c>
+      <c r="H12" t="s">
+        <v>654</v>
+      </c>
+      <c r="I12" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>585</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E13" t="str">
+        <f t="shared" si="0"/>
+        <v>'CPR01101'</v>
+      </c>
+      <c r="F13" t="s">
+        <v>654</v>
+      </c>
+      <c r="G13" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Premium Granel'</v>
+      </c>
+      <c r="H13" t="s">
+        <v>654</v>
+      </c>
+      <c r="I13" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>583</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E14" t="str">
+        <f t="shared" si="0"/>
+        <v>'CPR01102'</v>
+      </c>
+      <c r="F14" t="s">
+        <v>654</v>
+      </c>
+      <c r="G14" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Premium Tarima Chep'</v>
+      </c>
+      <c r="H14" t="s">
+        <v>654</v>
+      </c>
+      <c r="I14" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>595</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>596</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E15" t="str">
+        <f t="shared" si="0"/>
+        <v>'CPR01103'</v>
+      </c>
+      <c r="F15" t="s">
+        <v>654</v>
+      </c>
+      <c r="G15" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Premium Tarima Americana'</v>
+      </c>
+      <c r="H15" t="s">
+        <v>654</v>
+      </c>
+      <c r="I15" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>635</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E16" t="str">
+        <f t="shared" si="0"/>
+        <v>'CPR01104'</v>
+      </c>
+      <c r="F16" t="s">
+        <v>654</v>
+      </c>
+      <c r="G16" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Premium EUA Tarima Americana'</v>
+      </c>
+      <c r="H16" t="s">
+        <v>654</v>
+      </c>
+      <c r="I16" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>620</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>621</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E17" t="str">
+        <f t="shared" si="0"/>
+        <v>'CPR01106'</v>
+      </c>
+      <c r="F17" t="s">
+        <v>654</v>
+      </c>
+      <c r="G17" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Premium 22XU CP34 Union'</v>
+      </c>
+      <c r="H17" t="s">
+        <v>654</v>
+      </c>
+      <c r="I17" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>624</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>625</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E18" t="str">
+        <f t="shared" si="0"/>
+        <v>'CPR01107'</v>
+      </c>
+      <c r="F18" t="s">
+        <v>654</v>
+      </c>
+      <c r="G18" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Premium 22XU CP30 Union'</v>
+      </c>
+      <c r="H18" t="s">
+        <v>654</v>
+      </c>
+      <c r="I18" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>622</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E19" t="str">
+        <f t="shared" si="0"/>
+        <v>'CPR01108'</v>
+      </c>
+      <c r="F19" t="s">
+        <v>654</v>
+      </c>
+      <c r="G19" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Premium 22XU CP26 Union'</v>
+      </c>
+      <c r="H19" t="s">
+        <v>654</v>
+      </c>
+      <c r="I19" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>603</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E20" t="str">
+        <f t="shared" si="0"/>
+        <v>'CPR01109'</v>
+      </c>
+      <c r="F20" t="s">
+        <v>654</v>
+      </c>
+      <c r="G20" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Premium 22XU CP26 WR'</v>
+      </c>
+      <c r="H20" t="s">
+        <v>654</v>
+      </c>
+      <c r="I20" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>615</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>633</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E21" t="str">
+        <f t="shared" si="0"/>
+        <v>'CPR01111'</v>
+      </c>
+      <c r="F21" t="s">
+        <v>654</v>
+      </c>
+      <c r="G21" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Premium 22XU CP28 Royal'</v>
+      </c>
+      <c r="H21" t="s">
+        <v>654</v>
+      </c>
+      <c r="I21" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>618</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>619</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E22" t="str">
+        <f t="shared" si="0"/>
+        <v>'CPR01112'</v>
+      </c>
+      <c r="F22" t="s">
+        <v>654</v>
+      </c>
+      <c r="G22" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Premium 22XU CL25 Royal'</v>
+      </c>
+      <c r="H22" t="s">
+        <v>654</v>
+      </c>
+      <c r="I22" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>616</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E23" t="str">
+        <f t="shared" si="0"/>
+        <v>'CPR01113'</v>
+      </c>
+      <c r="F23" t="s">
+        <v>654</v>
+      </c>
+      <c r="G23" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Premium 22XU CL13 Royal'</v>
+      </c>
+      <c r="H23" t="s">
+        <v>654</v>
+      </c>
+      <c r="I23" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>645</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>646</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E24" t="str">
+        <f t="shared" si="0"/>
+        <v>'CPR01114'</v>
+      </c>
+      <c r="F24" t="s">
+        <v>654</v>
+      </c>
+      <c r="G24" t="str">
+        <f t="shared" si="1"/>
+        <v>'Platano de Chiapas BAE UPC 3237'</v>
+      </c>
+      <c r="H24" t="s">
+        <v>654</v>
+      </c>
+      <c r="I24" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>642</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>633</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E25" t="str">
+        <f t="shared" si="0"/>
+        <v>'CPR01115'</v>
+      </c>
+      <c r="F25" t="s">
+        <v>654</v>
+      </c>
+      <c r="G25" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Premium 22XU CP28 Royal'</v>
+      </c>
+      <c r="H25" t="s">
+        <v>654</v>
+      </c>
+      <c r="I25" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>647</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>632</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E26" t="str">
+        <f t="shared" si="0"/>
+        <v>'CPR01116'</v>
+      </c>
+      <c r="F26" t="s">
+        <v>654</v>
+      </c>
+      <c r="G26" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Premium 22XU CP26 Royal'</v>
+      </c>
+      <c r="H26" t="s">
+        <v>654</v>
+      </c>
+      <c r="I26" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>578</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E27" t="str">
+        <f t="shared" si="0"/>
+        <v>'CPR03117'</v>
+      </c>
+      <c r="F27" t="s">
+        <v>654</v>
+      </c>
+      <c r="G27" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Cha Cha Cha 22XU CP26 Mar Kodawari'</v>
+      </c>
+      <c r="H27" t="s">
+        <v>654</v>
+      </c>
+      <c r="I27" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>580</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E28" t="str">
+        <f t="shared" si="0"/>
+        <v>'CPR03119'</v>
+      </c>
+      <c r="F28" t="s">
+        <v>654</v>
+      </c>
+      <c r="G28" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Cha Cha Cha 22XU  CP34 Mar Kodawari'</v>
+      </c>
+      <c r="H28" t="s">
+        <v>654</v>
+      </c>
+      <c r="I28" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>597</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E29" t="str">
+        <f t="shared" si="0"/>
+        <v>'CPR03123'</v>
+      </c>
+      <c r="F29" t="s">
+        <v>654</v>
+      </c>
+      <c r="G29" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Premium Tarima Chep Banda 3b'</v>
+      </c>
+      <c r="H29" t="s">
+        <v>654</v>
+      </c>
+      <c r="I29" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>638</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>639</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E30" t="str">
+        <f t="shared" si="0"/>
+        <v>'CPR03124'</v>
+      </c>
+      <c r="F30" t="s">
+        <v>654</v>
+      </c>
+      <c r="G30" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Cha Cha Cha 22XU CP27 Mar Kodawari'</v>
+      </c>
+      <c r="H30" t="s">
+        <v>654</v>
+      </c>
+      <c r="I30" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>607</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>608</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E31" t="str">
+        <f t="shared" si="0"/>
+        <v>'CRG07125'</v>
+      </c>
+      <c r="F31" t="s">
+        <v>654</v>
+      </c>
+      <c r="G31" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Organic Banded Tape Verde'</v>
+      </c>
+      <c r="H31" t="s">
+        <v>654</v>
+      </c>
+      <c r="I31" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>609</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>610</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E32" t="str">
+        <f t="shared" si="0"/>
+        <v>'CRG07127'</v>
+      </c>
+      <c r="F32" t="s">
+        <v>654</v>
+      </c>
+      <c r="G32" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Organic 3lb Banded Tape Morado'</v>
+      </c>
+      <c r="H32" t="s">
+        <v>654</v>
+      </c>
+      <c r="I32" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>593</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E33" t="str">
+        <f t="shared" si="0"/>
+        <v>'CRG07128'</v>
+      </c>
+      <c r="F33" t="s">
+        <v>654</v>
+      </c>
+      <c r="G33" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Organic Banded Market Side Mexico'</v>
+      </c>
+      <c r="H33" t="s">
+        <v>654</v>
+      </c>
+      <c r="I33" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>605</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>606</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E34" t="str">
+        <f t="shared" si="0"/>
+        <v>'CRG07129'</v>
+      </c>
+      <c r="F34" t="s">
+        <v>654</v>
+      </c>
+      <c r="G34" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Organic Banded Market Side EUA'</v>
+      </c>
+      <c r="H34" t="s">
+        <v>654</v>
+      </c>
+      <c r="I34" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
         <v>613</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>614</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E35" t="str">
+        <f t="shared" si="0"/>
+        <v>'CRG07130'</v>
+      </c>
+      <c r="F35" t="s">
+        <v>654</v>
+      </c>
+      <c r="G35" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Organic  22XU CP28 Union'</v>
+      </c>
+      <c r="H35" t="s">
+        <v>654</v>
+      </c>
+      <c r="I35" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
         <v>611</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>612</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E36" t="str">
+        <f t="shared" si="0"/>
+        <v>'CRG07131'</v>
+      </c>
+      <c r="F36" t="s">
+        <v>654</v>
+      </c>
+      <c r="G36" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Organic  22XU CP34 Union'</v>
+      </c>
+      <c r="H36" t="s">
+        <v>654</v>
+      </c>
+      <c r="I36" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>626</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>629</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E37" t="str">
+        <f t="shared" si="0"/>
+        <v>'CRG07132'</v>
+      </c>
+      <c r="F37" t="s">
+        <v>654</v>
+      </c>
+      <c r="G37" t="str">
+        <f t="shared" si="1"/>
+        <v>'Organic  Wild Harvest '</v>
+      </c>
+      <c r="H37" t="s">
+        <v>654</v>
+      </c>
+      <c r="I37" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
         <v>640</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>641</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="E38" t="str">
+        <f t="shared" si="0"/>
+        <v>'CRG07133'</v>
+      </c>
+      <c r="F38" t="s">
+        <v>654</v>
+      </c>
+      <c r="G38" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Organic  Wild Harvest PLU94011'</v>
+      </c>
+      <c r="H38" t="s">
+        <v>654</v>
+      </c>
+      <c r="I38" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>587</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>588</v>
+      </c>
+      <c r="E39" t="str">
+        <f t="shared" si="0"/>
+        <v>'CSA04120'</v>
+      </c>
+      <c r="F39" t="s">
+        <v>654</v>
+      </c>
+      <c r="G39" t="str">
+        <f t="shared" si="1"/>
+        <v>'Chanitos Cha Cha Cha (2da) Granel'</v>
+      </c>
+      <c r="H39" t="s">
+        <v>654</v>
+      </c>
+      <c r="I39" t="s">
+        <v>692</v>
       </c>
     </row>
   </sheetData>
@@ -5985,4 +7059,583 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64F9C8D2-7547-4F48-9652-D384EE33666F}">
+  <dimension ref="A1:C51"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
+        <v>696</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>697</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>777</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>778</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>698</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>699</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
+        <v>704</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>705</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>761</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>762</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>769</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>770</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>783</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>784</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
+        <v>700</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>701</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>781</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>782</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
+        <v>742</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>743</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
+        <v>740</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>741</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
+        <v>694</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>695</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
+        <v>702</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>703</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
+        <v>736</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>737</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A16" s="12" t="s">
+        <v>748</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>749</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>750</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>751</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>750</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>754</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>759</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>760</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>779</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>780</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>779</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>785</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A22" s="12" t="s">
+        <v>710</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>711</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A23" s="12" t="s">
+        <v>714</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>715</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A24" s="12" t="s">
+        <v>718</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>719</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A25" s="12" t="s">
+        <v>746</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>747</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A26" s="12" t="s">
+        <v>712</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>713</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A27" s="12" t="s">
+        <v>722</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>723</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A28" s="12" t="s">
+        <v>706</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>707</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
+        <v>786</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>787</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A30" s="12" t="s">
+        <v>708</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>709</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A31" s="12" t="s">
+        <v>716</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>717</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A32" s="12" t="s">
+        <v>724</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>725</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A33" s="12" t="s">
+        <v>726</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A34" s="12" t="s">
+        <v>720</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>721</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>752</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>753</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>755</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>756</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>757</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>758</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
+        <v>763</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>764</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
+        <v>788</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>789</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>788</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>790</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A41" s="12" t="s">
+        <v>730</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>731</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A42" s="14" t="s">
+        <v>775</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>776</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A43" s="12" t="s">
+        <v>728</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>729</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A44" s="14" t="s">
+        <v>773</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>774</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A45" s="14" t="s">
+        <v>765</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>766</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A46" s="12" t="s">
+        <v>744</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>745</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
+        <v>771</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>772</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A48" s="12" t="s">
+        <v>732</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>733</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A49" s="13" t="s">
+        <v>734</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>735</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A50" s="14" t="s">
+        <v>767</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>768</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A51" s="13" t="s">
+        <v>738</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>739</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C51" xr:uid="{64F9C8D2-7547-4F48-9652-D384EE33666F}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C51">
+      <sortCondition ref="A1:A51"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Datos.xlsx
+++ b/Datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chanitosfrutas-my.sharepoint.com/personal/bescobedo_chanitos_com/Documents/WorkSpace/preenfrio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="189" documentId="13_ncr:1_{F0A36C04-E6E5-4B51-9906-23526A19135B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{488B2F12-BAE5-4B9D-897B-C12D4699D214}"/>
+  <xr:revisionPtr revIDLastSave="203" documentId="13_ncr:1_{F0A36C04-E6E5-4B51-9906-23526A19135B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34F0F59C-7F37-43D7-A858-2DBC6C68D99D}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{870F0A8F-B5CF-4FD7-9FD6-C646EB212759}"/>
   </bookViews>
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLIENTES-CEDIS'!$A$1:$C$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">FINCAS!$A$1:$G$284</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">FINCAS!$A$1:$O$284</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Hoja2!$A$1:$F$85</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">PRODUCTORES!$A$1:$C$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RANGOS TEMPERATURA'!$A$1:$C$1</definedName>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4946" uniqueCount="1344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4954" uniqueCount="1344">
   <si>
     <t>PREENFRIO</t>
   </si>
@@ -5435,7 +5435,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{329E6D9E-686A-4183-92BF-9B0AF16F6985}">
-  <dimension ref="A1:N284"/>
+  <dimension ref="A1:O284"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="57.7109375" bestFit="1" customWidth="1"/>
@@ -5446,7 +5446,7 @@
     <col min="8" max="10" width="11.42578125" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>94</v>
       </c>
@@ -5468,8 +5468,32 @@
       <c r="G1" s="3" t="s">
         <v>1126</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="H1" s="16" t="s">
+        <v>1119</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>1119</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>1119</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="M1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="N1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>131</v>
       </c>
@@ -5515,7 +5539,7 @@
         <v>('001','Marbella','FN_CHI_MARBELLA',1,80,1),</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>115</v>
       </c>
@@ -5561,7 +5585,7 @@
         <v>('002','Fortaleza','FN_CHI_FORTALEZA',1,80,1),</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>106</v>
       </c>
@@ -5607,7 +5631,7 @@
         <v>('003','Doña Nelly','FN_CHI_DONA_NELLY',1,80,1),</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>123</v>
       </c>
@@ -5653,7 +5677,7 @@
         <v>('004','La Ceiba','FN_CHI_LA_CEIBA',1,80,1),</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>534</v>
       </c>
@@ -5699,7 +5723,7 @@
         <v>('026','Santa Fe','FN_CHI_STAFE',1,82,1),</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>532</v>
       </c>
@@ -5745,7 +5769,7 @@
         <v>('027','El Cahua','FN_CHI_ELCAHUA',1,82,1),</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>557</v>
       </c>
@@ -5791,7 +5815,7 @@
         <v>('028','Romina','FN_CHI_ROMINA',1,82,1),</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>117</v>
       </c>
@@ -5837,7 +5861,7 @@
         <v>('005','La Gloria','FN_CHI_GLORIA',1,83,1),</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>98</v>
       </c>
@@ -5883,7 +5907,7 @@
         <v>('033','Carlota Nava','FN_CHI_CARLOTA',1,83,1),</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>146</v>
       </c>
@@ -5929,7 +5953,7 @@
         <v>('038','El Triunfo Nava','FN_CHI_TRIUNFONAV',1,83,1),</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>144</v>
       </c>
@@ -5975,7 +5999,7 @@
         <v>('083','Santa Maria','FN_CHI_SANTA_MARIA',1,83,1),</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>127</v>
       </c>
@@ -6021,7 +6045,7 @@
         <v>('084','Lisboa','FN_CHI_LISBOA',1,83,1),</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>479</v>
       </c>
@@ -6067,7 +6091,7 @@
         <v>('098','Trinidad y Lindavista','FN_CHI_TRINIDAD',1,83,1),</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>137</v>
       </c>
@@ -6113,7 +6137,7 @@
         <v>('040','Plataneros Unidos 1','FN_CHI_PLATANEROS1',1,84,1),</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>139</v>
       </c>
@@ -18522,7 +18546,7 @@
     <protectedRange algorithmName="SHA-512" hashValue="oAofLzPsEABz+g8s4EYjUuwXH7ykbMbBHfCBkrjaG9AypkvLlHymmath48lOXQru/nByDYQVi/KXn1fge9PtNA==" saltValue="K19iw11Oiq05wm1mPIKVDQ==" spinCount="100000" sqref="D276" name="Rango4_30"/>
     <protectedRange algorithmName="SHA-512" hashValue="oAofLzPsEABz+g8s4EYjUuwXH7ykbMbBHfCBkrjaG9AypkvLlHymmath48lOXQru/nByDYQVi/KXn1fge9PtNA==" saltValue="K19iw11Oiq05wm1mPIKVDQ==" spinCount="100000" sqref="D277" name="Rango4_31"/>
   </protectedRanges>
-  <autoFilter ref="A1:G284" xr:uid="{329E6D9E-686A-4183-92BF-9B0AF16F6985}"/>
+  <autoFilter ref="A1:O284" xr:uid="{329E6D9E-686A-4183-92BF-9B0AF16F6985}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Datos.xlsx
+++ b/Datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chanitosfrutas-my.sharepoint.com/personal/bescobedo_chanitos_com/Documents/WorkSpace/preenfrio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="203" documentId="13_ncr:1_{F0A36C04-E6E5-4B51-9906-23526A19135B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34F0F59C-7F37-43D7-A858-2DBC6C68D99D}"/>
+  <xr:revisionPtr revIDLastSave="211" documentId="13_ncr:1_{F0A36C04-E6E5-4B51-9906-23526A19135B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60DC4AD8-788F-496F-920E-5072183C54F4}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{870F0A8F-B5CF-4FD7-9FD6-C646EB212759}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{870F0A8F-B5CF-4FD7-9FD6-C646EB212759}"/>
   </bookViews>
   <sheets>
     <sheet name="PREENFRIO" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4954" uniqueCount="1344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5118" uniqueCount="1344">
   <si>
     <t>PREENFRIO</t>
   </si>
@@ -4167,7 +4167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4218,6 +4218,9 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4766,7 +4769,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7041A0F3-0727-46BE-AF1B-1333F80826B4}">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.5703125" customWidth="1"/>
@@ -4774,7 +4777,7 @@
     <col min="3" max="3" width="27.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>56</v>
       </c>
@@ -4785,7 +4788,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>32</v>
       </c>
@@ -4795,8 +4798,24 @@
       <c r="C2" s="5" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D2" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H2" t="str">
+        <f>+D2&amp;E2&amp;A2&amp;E2&amp;F2&amp;E2&amp;B2&amp;E2&amp;F2&amp;E2&amp;C2&amp;E2&amp;G2&amp;F2</f>
+        <v>('CEDIS CHIHUAHUA','CHIHUAHUA','CHH'),</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>29</v>
       </c>
@@ -4806,8 +4825,24 @@
       <c r="C3" s="5" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D3" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H42" si="0">+D3&amp;E3&amp;A3&amp;E3&amp;F3&amp;E3&amp;B3&amp;E3&amp;F3&amp;E3&amp;C3&amp;E3&amp;G3&amp;F3</f>
+        <v>('CENTRAL DE ABASTO','IZTAPALAPA','CEDA IZT'),</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>29</v>
       </c>
@@ -4817,8 +4852,24 @@
       <c r="C4" s="5" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D4" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H4" t="str">
+        <f t="shared" si="0"/>
+        <v>('CENTRAL DE ABASTO','TULTITLAN','CEDA TULTI'),</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>39</v>
       </c>
@@ -4828,8 +4879,24 @@
       <c r="C5" s="5" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D5" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H5" t="str">
+        <f t="shared" si="0"/>
+        <v>('CENTRAL PLATANERA','CIUDAD JUAREZ','CDA JUAREZ'),</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>34</v>
       </c>
@@ -4839,8 +4906,24 @@
       <c r="C6" s="5" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D6" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" si="0"/>
+        <v>('CHANITOS INTERNATIONAL','MC ALLEN','MC ALLEN INT'),</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>38</v>
       </c>
@@ -4850,8 +4933,24 @@
       <c r="C7" s="5" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D7" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="0"/>
+        <v>('CHEDRAUI','ZUMPANGO','CHEDRAUI ZUM'),</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>33</v>
       </c>
@@ -4861,8 +4960,24 @@
       <c r="C8" s="5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D8" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="0"/>
+        <v>('JAPON','JAPON','JAPON'),</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>25</v>
       </c>
@@ -4872,8 +4987,24 @@
       <c r="C9" s="5" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D9" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="0"/>
+        <v>('LOCAL','TAPACHULA','LOCAL TAP'),</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>25</v>
       </c>
@@ -4883,8 +5014,24 @@
       <c r="C10" s="5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D10" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="0"/>
+        <v>('LOCAL','COLIMA','LOCAL COL'),</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>25</v>
       </c>
@@ -4894,8 +5041,24 @@
       <c r="C11" s="5" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D11" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="0"/>
+        <v>('LOCAL','TABASCO','LOCAL TAB'),</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>31</v>
       </c>
@@ -4905,8 +5068,24 @@
       <c r="C12" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D12" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="0"/>
+        <v>('NUEVA WALMART','CHALCO','WM CHALCO'),</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>31</v>
       </c>
@@ -4916,8 +5095,24 @@
       <c r="C13" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D13" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H13" t="str">
+        <f t="shared" si="0"/>
+        <v>('NUEVA WALMART','CULIACAN','WM CLN'),</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>31</v>
       </c>
@@ -4927,8 +5122,24 @@
       <c r="C14" s="5" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D14" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H14" t="str">
+        <f t="shared" si="0"/>
+        <v>('NUEVA WALMART','GUADALAJARA','WM GDL'),</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>31</v>
       </c>
@@ -4938,8 +5149,24 @@
       <c r="C15" s="5" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D15" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" si="0"/>
+        <v>('NUEVA WALMART','MONTERREY','WM MTY'),</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>31</v>
       </c>
@@ -4949,8 +5176,24 @@
       <c r="C16" s="5" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D16" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H16" t="str">
+        <f t="shared" si="0"/>
+        <v>('NUEVA WALMART','QUERETARO','WM QRO'),</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>31</v>
       </c>
@@ -4960,8 +5203,24 @@
       <c r="C17" s="5" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D17" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" si="0"/>
+        <v>('NUEVA WALMART','SAN MARTIN DE OBISPO','WM SMO'),</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>31</v>
       </c>
@@ -4971,8 +5230,24 @@
       <c r="C18" s="5" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D18" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H18" t="str">
+        <f t="shared" si="0"/>
+        <v>('NUEVA WALMART','VILLAHERMOSA','WM VSA'),</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>36</v>
       </c>
@@ -4982,8 +5257,24 @@
       <c r="C19" s="5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D19" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="0"/>
+        <v>('PATROCINIO','PATROCINIO','PATROCINIO'),</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>30</v>
       </c>
@@ -4993,8 +5284,24 @@
       <c r="C20" s="5" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D20" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H20" t="str">
+        <f t="shared" si="0"/>
+        <v>('S-MART','CIUDAD JUAREZ','S-MART CD JUAREZ'),</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>30</v>
       </c>
@@ -5004,8 +5311,24 @@
       <c r="C21" s="5" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D21" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H21" t="str">
+        <f t="shared" si="0"/>
+        <v>('S-MART','MONTERREY','S-MART MTY'),</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
@@ -5015,8 +5338,24 @@
       <c r="C22" s="5" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D22" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H22" t="str">
+        <f t="shared" si="0"/>
+        <v>('SORIANA','SORIANA','SORIANA'),</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>52</v>
       </c>
@@ -5026,8 +5365,24 @@
       <c r="C23" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D23" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H23" t="str">
+        <f t="shared" si="0"/>
+        <v>('TAPACHULA','TAPACHULA','TAPACHULA'),</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>35</v>
       </c>
@@ -5037,92 +5392,220 @@
       <c r="C24" s="5" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D24" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H24" t="str">
+        <f t="shared" si="0"/>
+        <v>('UNITED NATURAL FOODS, INC','MC ALLEN','MC ALLEN UNFI'),</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B25" s="5" t="str">
-        <f t="shared" ref="B25:B31" si="0">+A12&amp;"-"&amp;B12</f>
+        <f t="shared" ref="B25:B31" si="1">+A12&amp;"-"&amp;B12</f>
         <v>NUEVA WALMART-CHALCO</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D25" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H25" t="str">
+        <f t="shared" si="0"/>
+        <v>('RECHAZO','NUEVA WALMART-CHALCO','RECHAZO WM CHALCO'),</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B26" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NUEVA WALMART-CULIACAN</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D26" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H26" t="str">
+        <f t="shared" si="0"/>
+        <v>('RECHAZO','NUEVA WALMART-CULIACAN','RECHAZO WM CLN'),</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B27" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NUEVA WALMART-GUADALAJARA</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D27" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H27" t="str">
+        <f t="shared" si="0"/>
+        <v>('RECHAZO','NUEVA WALMART-GUADALAJARA','RECHAZO WM GDL'),</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B28" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NUEVA WALMART-MONTERREY</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D28" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H28" t="str">
+        <f t="shared" si="0"/>
+        <v>('RECHAZO','NUEVA WALMART-MONTERREY','RECHAZO WM MTY'),</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B29" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NUEVA WALMART-QUERETARO</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D29" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H29" t="str">
+        <f t="shared" si="0"/>
+        <v>('RECHAZO','NUEVA WALMART-QUERETARO','RECHAZO WM QRO'),</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B30" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NUEVA WALMART-SAN MARTIN DE OBISPO</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D30" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H30" t="str">
+        <f t="shared" si="0"/>
+        <v>('RECHAZO','NUEVA WALMART-SAN MARTIN DE OBISPO','RECHAZO WM SMO'),</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B31" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>NUEVA WALMART-VILLAHERMOSA</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D31" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H31" t="str">
+        <f t="shared" si="0"/>
+        <v>('RECHAZO','NUEVA WALMART-VILLAHERMOSA','RECHAZO WM VSA'),</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>24</v>
       </c>
@@ -5133,8 +5616,24 @@
       <c r="C32" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D32" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H32" t="str">
+        <f t="shared" si="0"/>
+        <v>('RECHAZO','S-MART-CIUDAD JUAREZ','RECHAZO S-MART CD JUAREZ'),</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>24</v>
       </c>
@@ -5145,8 +5644,24 @@
       <c r="C33" s="5" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D33" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H33" t="str">
+        <f t="shared" si="0"/>
+        <v>('RECHAZO','S-MART-MONTERREY','RECHAZO S-MART MTY'),</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>24</v>
       </c>
@@ -5157,8 +5672,24 @@
       <c r="C34" s="5" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D34" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H34" t="str">
+        <f t="shared" si="0"/>
+        <v>('RECHAZO','SORIANA','RECHAZO SORIANA'),</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>24</v>
       </c>
@@ -5169,8 +5700,24 @@
       <c r="C35" s="5" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D35" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E35" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H35" t="str">
+        <f t="shared" si="0"/>
+        <v>('RECHAZO','MC ALLEN','RECHAZO MC ALLEN UNFI'),</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>24</v>
       </c>
@@ -5181,8 +5728,24 @@
       <c r="C36" s="5" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D36" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H36" t="str">
+        <f t="shared" si="0"/>
+        <v>('RECHAZO','CHEDRAUI-ZUMPANGO','RECHAZO CHEDRAUI ZUM'),</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>27</v>
       </c>
@@ -5193,8 +5756,24 @@
       <c r="C37" s="5" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D37" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H37" t="str">
+        <f t="shared" si="0"/>
+        <v>('MATERIALES','TAPACHULA','MATERIALES TAP'),</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>27</v>
       </c>
@@ -5205,8 +5784,24 @@
       <c r="C38" s="5" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D38" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H38" t="str">
+        <f t="shared" si="0"/>
+        <v>('MATERIALES','COLIMA','MATERIALES COL'),</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>27</v>
       </c>
@@ -5217,8 +5812,24 @@
       <c r="C39" s="5" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D39" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H39" t="str">
+        <f t="shared" si="0"/>
+        <v>('MATERIALES','TABASCO','MATERIALES TAB'),</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>26</v>
       </c>
@@ -5229,29 +5840,77 @@
       <c r="C40" s="5" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D40" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H40" t="str">
+        <f t="shared" si="0"/>
+        <v>('TARIMAS','TAPACHULA','TARIMAS TAP'),</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B41" s="5" t="str">
-        <f t="shared" ref="B41:B42" si="1">+B10</f>
+        <f t="shared" ref="B41:B42" si="2">+B10</f>
         <v>COLIMA</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D41" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E41" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H41" t="str">
+        <f t="shared" si="0"/>
+        <v>('TARIMAS','COLIMA','TARIMAS COL'),</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B42" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>TABASCO</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>93</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="H42" t="str">
+        <f t="shared" si="0"/>
+        <v>('TARIMAS','TABASCO','TARIMAS TAB'),</v>
       </c>
     </row>
   </sheetData>

--- a/Datos.xlsx
+++ b/Datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chanitosfrutas-my.sharepoint.com/personal/bescobedo_chanitos_com/Documents/WorkSpace/preenfrio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="265" documentId="13_ncr:1_{F0A36C04-E6E5-4B51-9906-23526A19135B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3441DBD5-1E80-41A3-B380-0A637444FF1A}"/>
+  <xr:revisionPtr revIDLastSave="311" documentId="13_ncr:1_{F0A36C04-E6E5-4B51-9906-23526A19135B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E3B267F-3F95-4AD3-B07C-FE818ADA9922}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{870F0A8F-B5CF-4FD7-9FD6-C646EB212759}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{870F0A8F-B5CF-4FD7-9FD6-C646EB212759}"/>
   </bookViews>
   <sheets>
     <sheet name="PREENFRIO" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Hoja2!$A$1:$F$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">PRODUCTORES!$A$1:$C$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RANGOS TEMPERATURA'!$A$1:$C$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">SKU!$A$1:$B$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">SKU!$B$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5119" uniqueCount="1345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5121" uniqueCount="1347">
   <si>
     <t>PREENFRIO</t>
   </si>
@@ -4088,6 +4088,12 @@
   </si>
   <si>
     <t>CELESTE MORENO</t>
+  </si>
+  <si>
+    <t>TURNO</t>
+  </si>
+  <si>
+    <t>ID</t>
   </si>
 </sst>
 </file>
@@ -4226,7 +4232,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -20481,1130 +20497,1363 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{961DD99E-A2C7-4E25-8FB0-84DFB4FA4937}">
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:P39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="68.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="68.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="D1" s="3" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>648</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="8" t="s">
         <v>582</v>
       </c>
-      <c r="E2" t="str">
-        <f>+"'"&amp;A2&amp;"'"</f>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="I2" t="str">
+        <f>+"'"&amp;B2&amp;"'"</f>
         <v>'CDS06124'</v>
       </c>
-      <c r="F2" t="s">
-        <v>654</v>
-      </c>
-      <c r="G2" t="str">
-        <f>+"'"&amp;B2&amp;"'"</f>
+      <c r="J2" t="s">
+        <v>654</v>
+      </c>
+      <c r="K2" t="str">
+        <f>+"'"&amp;C2&amp;"'"</f>
         <v>'Chanitos Snack'</v>
       </c>
-      <c r="H2" t="s">
-        <v>654</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="L2" t="s">
+        <v>654</v>
+      </c>
+      <c r="M2" t="s">
         <v>655</v>
       </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="P2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="E3" t="str">
-        <f t="shared" ref="E3:E39" si="0">+"'"&amp;A3&amp;"'"</f>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" ref="I3:I39" si="0">+"'"&amp;B3&amp;"'"</f>
         <v>'CCL02114'</v>
       </c>
-      <c r="F3" t="s">
-        <v>654</v>
-      </c>
-      <c r="G3" t="str">
-        <f t="shared" ref="G3:G39" si="1">+"'"&amp;B3&amp;"'"</f>
+      <c r="J3" t="s">
+        <v>654</v>
+      </c>
+      <c r="K3" t="str">
+        <f t="shared" ref="K3:K39" si="1">+"'"&amp;C3&amp;"'"</f>
         <v>'Chanitos Classic Granel'</v>
       </c>
-      <c r="H3" t="s">
-        <v>654</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="L3" t="s">
+        <v>654</v>
+      </c>
+      <c r="M3" t="s">
         <v>656</v>
       </c>
-      <c r="L3">
-        <f>+L2+1</f>
+      <c r="P3">
+        <f>+P2+1</f>
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>634</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="8" t="s">
         <v>637</v>
       </c>
-      <c r="E4" t="str">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="I4" t="str">
         <f t="shared" si="0"/>
         <v>'CDM10137'</v>
       </c>
-      <c r="F4" t="s">
-        <v>654</v>
-      </c>
-      <c r="G4" t="str">
+      <c r="J4" t="s">
+        <v>654</v>
+      </c>
+      <c r="K4" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Dominico 1ra'</v>
       </c>
-      <c r="H4" t="s">
-        <v>654</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
+        <v>654</v>
+      </c>
+      <c r="M4" t="s">
         <v>657</v>
       </c>
-      <c r="L4">
-        <f t="shared" ref="L4:L39" si="2">+L3+1</f>
+      <c r="P4">
+        <f t="shared" ref="P4:P39" si="2">+P3+1</f>
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="7">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>627</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>628</v>
       </c>
-      <c r="E5" t="str">
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="I5" t="str">
         <f t="shared" si="0"/>
         <v>'CDM10138'</v>
       </c>
-      <c r="F5" t="s">
-        <v>654</v>
-      </c>
-      <c r="G5" t="str">
+      <c r="J5" t="s">
+        <v>654</v>
+      </c>
+      <c r="K5" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Dominico 2da'</v>
       </c>
-      <c r="H5" t="s">
-        <v>654</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="L5" t="s">
+        <v>654</v>
+      </c>
+      <c r="M5" t="s">
         <v>658</v>
       </c>
-      <c r="L5">
+      <c r="P5">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+    <row r="6" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="7">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>591</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="C6" s="8" t="s">
         <v>592</v>
       </c>
-      <c r="E6" t="str">
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="I6" t="str">
         <f t="shared" si="0"/>
         <v>'CDS04122'</v>
       </c>
-      <c r="F6" t="s">
-        <v>654</v>
-      </c>
-      <c r="G6" t="str">
+      <c r="J6" t="s">
+        <v>654</v>
+      </c>
+      <c r="K6" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Cha Cha Cha (DS) Granel'</v>
       </c>
-      <c r="H6" t="s">
-        <v>654</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="L6" t="s">
+        <v>654</v>
+      </c>
+      <c r="M6" t="s">
         <v>659</v>
       </c>
-      <c r="L6">
+      <c r="P6">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+    <row r="7" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>643</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="C7" s="8" t="s">
         <v>586</v>
       </c>
-      <c r="E7" t="str">
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="I7" t="str">
         <f t="shared" si="0"/>
         <v>'CDS04123'</v>
       </c>
-      <c r="F7" t="s">
-        <v>654</v>
-      </c>
-      <c r="G7" t="str">
+      <c r="J7" t="s">
+        <v>654</v>
+      </c>
+      <c r="K7" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Premium Granel'</v>
       </c>
-      <c r="H7" t="s">
-        <v>654</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="L7" t="s">
+        <v>654</v>
+      </c>
+      <c r="M7" t="s">
         <v>660</v>
       </c>
-      <c r="L7">
+      <c r="P7">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+    <row r="8" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>644</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="8" t="s">
         <v>584</v>
       </c>
-      <c r="E8" t="str">
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="I8" t="str">
         <f t="shared" si="0"/>
         <v>'CDS04125'</v>
       </c>
-      <c r="F8" t="s">
-        <v>654</v>
-      </c>
-      <c r="G8" t="str">
+      <c r="J8" t="s">
+        <v>654</v>
+      </c>
+      <c r="K8" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Premium Tarima Chep'</v>
       </c>
-      <c r="H8" t="s">
-        <v>654</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="L8" t="s">
+        <v>654</v>
+      </c>
+      <c r="M8" t="s">
         <v>661</v>
       </c>
-      <c r="L8">
+      <c r="P8">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
+    <row r="9" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="7">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>589</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="C9" s="8" t="s">
         <v>590</v>
       </c>
-      <c r="E9" t="str">
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="I9" t="str">
         <f t="shared" si="0"/>
         <v>'CMN05123'</v>
       </c>
-      <c r="F9" t="s">
-        <v>654</v>
-      </c>
-      <c r="G9" t="str">
+      <c r="J9" t="s">
+        <v>654</v>
+      </c>
+      <c r="K9" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Manitas Granel'</v>
       </c>
-      <c r="H9" t="s">
-        <v>654</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="L9" t="s">
+        <v>654</v>
+      </c>
+      <c r="M9" t="s">
         <v>662</v>
       </c>
-      <c r="L9">
+      <c r="P9">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="7">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>576</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="C10" s="8" t="s">
         <v>577</v>
       </c>
-      <c r="E10" t="str">
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="I10" t="str">
         <f t="shared" si="0"/>
         <v>'CPL08133'</v>
       </c>
-      <c r="F10" t="s">
-        <v>654</v>
-      </c>
-      <c r="G10" t="str">
+      <c r="J10" t="s">
+        <v>654</v>
+      </c>
+      <c r="K10" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Plantain 50lb Tarima Americana'</v>
       </c>
-      <c r="H10" t="s">
-        <v>654</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="L10" t="s">
+        <v>654</v>
+      </c>
+      <c r="M10" t="s">
         <v>663</v>
       </c>
-      <c r="L10">
+      <c r="P10">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="7">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>599</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="C11" s="8" t="s">
         <v>600</v>
       </c>
-      <c r="E11" t="str">
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="I11" t="str">
         <f t="shared" si="0"/>
         <v>'CPL08134'</v>
       </c>
-      <c r="F11" t="s">
-        <v>654</v>
-      </c>
-      <c r="G11" t="str">
+      <c r="J11" t="s">
+        <v>654</v>
+      </c>
+      <c r="K11" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Plantain 20Kg Tarima Americana'</v>
       </c>
-      <c r="H11" t="s">
-        <v>654</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="L11" t="s">
+        <v>654</v>
+      </c>
+      <c r="M11" t="s">
         <v>664</v>
       </c>
-      <c r="L11">
+      <c r="P11">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="7">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>601</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="C12" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="E12" t="str">
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="I12" t="str">
         <f t="shared" si="0"/>
         <v>'CPL08141'</v>
       </c>
-      <c r="F12" t="s">
-        <v>654</v>
-      </c>
-      <c r="G12" t="str">
+      <c r="J12" t="s">
+        <v>654</v>
+      </c>
+      <c r="K12" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Plantain 20Kg Tarima Chep'</v>
       </c>
-      <c r="H12" t="s">
-        <v>654</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="L12" t="s">
+        <v>654</v>
+      </c>
+      <c r="M12" t="s">
         <v>665</v>
       </c>
-      <c r="L12">
+      <c r="P12">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="7">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>585</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="C13" s="8" t="s">
         <v>586</v>
       </c>
-      <c r="E13" t="str">
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="I13" t="str">
         <f t="shared" si="0"/>
         <v>'CPR01101'</v>
       </c>
-      <c r="F13" t="s">
-        <v>654</v>
-      </c>
-      <c r="G13" t="str">
+      <c r="J13" t="s">
+        <v>654</v>
+      </c>
+      <c r="K13" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Premium Granel'</v>
       </c>
-      <c r="H13" t="s">
-        <v>654</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="L13" t="s">
+        <v>654</v>
+      </c>
+      <c r="M13" t="s">
         <v>666</v>
       </c>
-      <c r="L13">
+      <c r="P13">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="7">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>583</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="C14" s="8" t="s">
         <v>584</v>
       </c>
-      <c r="E14" t="str">
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="I14" t="str">
         <f t="shared" si="0"/>
         <v>'CPR01102'</v>
       </c>
-      <c r="F14" t="s">
-        <v>654</v>
-      </c>
-      <c r="G14" t="str">
+      <c r="J14" t="s">
+        <v>654</v>
+      </c>
+      <c r="K14" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Premium Tarima Chep'</v>
       </c>
-      <c r="H14" t="s">
-        <v>654</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="L14" t="s">
+        <v>654</v>
+      </c>
+      <c r="M14" t="s">
         <v>667</v>
       </c>
-      <c r="L14">
+      <c r="P14">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A15" s="7">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>595</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="C15" s="8" t="s">
         <v>596</v>
       </c>
-      <c r="E15" t="str">
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="I15" t="str">
         <f t="shared" si="0"/>
         <v>'CPR01103'</v>
       </c>
-      <c r="F15" t="s">
-        <v>654</v>
-      </c>
-      <c r="G15" t="str">
+      <c r="J15" t="s">
+        <v>654</v>
+      </c>
+      <c r="K15" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Premium Tarima Americana'</v>
       </c>
-      <c r="H15" t="s">
-        <v>654</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="L15" t="s">
+        <v>654</v>
+      </c>
+      <c r="M15" t="s">
         <v>668</v>
       </c>
-      <c r="L15">
+      <c r="P15">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+    <row r="16" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>635</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="C16" s="8" t="s">
         <v>636</v>
       </c>
-      <c r="E16" t="str">
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="I16" t="str">
         <f t="shared" si="0"/>
         <v>'CPR01104'</v>
       </c>
-      <c r="F16" t="s">
-        <v>654</v>
-      </c>
-      <c r="G16" t="str">
+      <c r="J16" t="s">
+        <v>654</v>
+      </c>
+      <c r="K16" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Premium EUA Tarima Americana'</v>
       </c>
-      <c r="H16" t="s">
-        <v>654</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="L16" t="s">
+        <v>654</v>
+      </c>
+      <c r="M16" t="s">
         <v>669</v>
       </c>
-      <c r="L16">
+      <c r="P16">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A17" s="7">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>620</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="C17" s="8" t="s">
         <v>621</v>
       </c>
-      <c r="E17" t="str">
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="I17" t="str">
         <f t="shared" si="0"/>
         <v>'CPR01106'</v>
       </c>
-      <c r="F17" t="s">
-        <v>654</v>
-      </c>
-      <c r="G17" t="str">
+      <c r="J17" t="s">
+        <v>654</v>
+      </c>
+      <c r="K17" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Premium 22XU CP34 Union'</v>
       </c>
-      <c r="H17" t="s">
-        <v>654</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="L17" t="s">
+        <v>654</v>
+      </c>
+      <c r="M17" t="s">
         <v>670</v>
       </c>
-      <c r="L17">
+      <c r="P17">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A18" s="7">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>624</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="C18" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="E18" t="str">
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="I18" t="str">
         <f t="shared" si="0"/>
         <v>'CPR01107'</v>
       </c>
-      <c r="F18" t="s">
-        <v>654</v>
-      </c>
-      <c r="G18" t="str">
+      <c r="J18" t="s">
+        <v>654</v>
+      </c>
+      <c r="K18" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Premium 22XU CP30 Union'</v>
       </c>
-      <c r="H18" t="s">
-        <v>654</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="L18" t="s">
+        <v>654</v>
+      </c>
+      <c r="M18" t="s">
         <v>671</v>
       </c>
-      <c r="L18">
+      <c r="P18">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A19" s="7">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>622</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="C19" s="8" t="s">
         <v>623</v>
       </c>
-      <c r="E19" t="str">
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="I19" t="str">
         <f t="shared" si="0"/>
         <v>'CPR01108'</v>
       </c>
-      <c r="F19" t="s">
-        <v>654</v>
-      </c>
-      <c r="G19" t="str">
+      <c r="J19" t="s">
+        <v>654</v>
+      </c>
+      <c r="K19" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Premium 22XU CP26 Union'</v>
       </c>
-      <c r="H19" t="s">
-        <v>654</v>
-      </c>
-      <c r="I19" t="s">
+      <c r="L19" t="s">
+        <v>654</v>
+      </c>
+      <c r="M19" t="s">
         <v>672</v>
       </c>
-      <c r="L19">
+      <c r="P19">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="7">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>603</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="C20" s="8" t="s">
         <v>604</v>
       </c>
-      <c r="E20" t="str">
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="I20" t="str">
         <f t="shared" si="0"/>
         <v>'CPR01109'</v>
       </c>
-      <c r="F20" t="s">
-        <v>654</v>
-      </c>
-      <c r="G20" t="str">
+      <c r="J20" t="s">
+        <v>654</v>
+      </c>
+      <c r="K20" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Premium 22XU CP26 WR'</v>
       </c>
-      <c r="H20" t="s">
-        <v>654</v>
-      </c>
-      <c r="I20" t="s">
+      <c r="L20" t="s">
+        <v>654</v>
+      </c>
+      <c r="M20" t="s">
         <v>673</v>
       </c>
-      <c r="L20">
+      <c r="P20">
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A21" s="7">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>615</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="C21" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="E21" t="str">
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="I21" t="str">
         <f t="shared" si="0"/>
         <v>'CPR01111'</v>
       </c>
-      <c r="F21" t="s">
-        <v>654</v>
-      </c>
-      <c r="G21" t="str">
+      <c r="J21" t="s">
+        <v>654</v>
+      </c>
+      <c r="K21" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Premium 22XU CP28 Royal'</v>
       </c>
-      <c r="H21" t="s">
-        <v>654</v>
-      </c>
-      <c r="I21" t="s">
+      <c r="L21" t="s">
+        <v>654</v>
+      </c>
+      <c r="M21" t="s">
         <v>674</v>
       </c>
-      <c r="L21">
+      <c r="P21">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A22" s="7">
+        <v>21</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>618</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="C22" s="8" t="s">
         <v>619</v>
       </c>
-      <c r="E22" t="str">
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="I22" t="str">
         <f t="shared" si="0"/>
         <v>'CPR01112'</v>
       </c>
-      <c r="F22" t="s">
-        <v>654</v>
-      </c>
-      <c r="G22" t="str">
+      <c r="J22" t="s">
+        <v>654</v>
+      </c>
+      <c r="K22" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Premium 22XU CL25 Royal'</v>
       </c>
-      <c r="H22" t="s">
-        <v>654</v>
-      </c>
-      <c r="I22" t="s">
+      <c r="L22" t="s">
+        <v>654</v>
+      </c>
+      <c r="M22" t="s">
         <v>675</v>
       </c>
-      <c r="L22">
+      <c r="P22">
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
+    <row r="23" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A23" s="7">
+        <v>22</v>
+      </c>
+      <c r="B23" s="7" t="s">
         <v>616</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="C23" s="8" t="s">
         <v>617</v>
       </c>
-      <c r="E23" t="str">
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="I23" t="str">
         <f t="shared" si="0"/>
         <v>'CPR01113'</v>
       </c>
-      <c r="F23" t="s">
-        <v>654</v>
-      </c>
-      <c r="G23" t="str">
+      <c r="J23" t="s">
+        <v>654</v>
+      </c>
+      <c r="K23" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Premium 22XU CL13 Royal'</v>
       </c>
-      <c r="H23" t="s">
-        <v>654</v>
-      </c>
-      <c r="I23" t="s">
+      <c r="L23" t="s">
+        <v>654</v>
+      </c>
+      <c r="M23" t="s">
         <v>676</v>
       </c>
-      <c r="L23">
+      <c r="P23">
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+    <row r="24" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A24" s="8">
+        <v>23</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>645</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="C24" s="9" t="s">
         <v>646</v>
       </c>
-      <c r="E24" t="str">
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="I24" t="str">
         <f t="shared" si="0"/>
         <v>'CPR01114'</v>
       </c>
-      <c r="F24" t="s">
-        <v>654</v>
-      </c>
-      <c r="G24" t="str">
+      <c r="J24" t="s">
+        <v>654</v>
+      </c>
+      <c r="K24" t="str">
         <f t="shared" si="1"/>
         <v>'Platano de Chiapas BAE UPC 3237'</v>
       </c>
-      <c r="H24" t="s">
-        <v>654</v>
-      </c>
-      <c r="I24" t="s">
+      <c r="L24" t="s">
+        <v>654</v>
+      </c>
+      <c r="M24" t="s">
         <v>677</v>
       </c>
-      <c r="L24">
+      <c r="P24">
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+    <row r="25" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A25" s="8">
+        <v>24</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>642</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="C25" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="E25" t="str">
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="I25" t="str">
         <f t="shared" si="0"/>
         <v>'CPR01115'</v>
       </c>
-      <c r="F25" t="s">
-        <v>654</v>
-      </c>
-      <c r="G25" t="str">
+      <c r="J25" t="s">
+        <v>654</v>
+      </c>
+      <c r="K25" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Premium 22XU CP28 Royal'</v>
       </c>
-      <c r="H25" t="s">
-        <v>654</v>
-      </c>
-      <c r="I25" t="s">
+      <c r="L25" t="s">
+        <v>654</v>
+      </c>
+      <c r="M25" t="s">
         <v>678</v>
       </c>
-      <c r="L25">
+      <c r="P25">
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+    <row r="26" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A26" s="8">
+        <v>25</v>
+      </c>
+      <c r="B26" s="8" t="s">
         <v>647</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="C26" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="E26" t="str">
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="I26" t="str">
         <f t="shared" si="0"/>
         <v>'CPR01116'</v>
       </c>
-      <c r="F26" t="s">
-        <v>654</v>
-      </c>
-      <c r="G26" t="str">
+      <c r="J26" t="s">
+        <v>654</v>
+      </c>
+      <c r="K26" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Premium 22XU CP26 Royal'</v>
       </c>
-      <c r="H26" t="s">
-        <v>654</v>
-      </c>
-      <c r="I26" t="s">
+      <c r="L26" t="s">
+        <v>654</v>
+      </c>
+      <c r="M26" t="s">
         <v>679</v>
       </c>
-      <c r="L26">
+      <c r="P26">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
+    <row r="27" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A27" s="7">
+        <v>26</v>
+      </c>
+      <c r="B27" s="7" t="s">
         <v>578</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="C27" s="8" t="s">
         <v>579</v>
       </c>
-      <c r="E27" t="str">
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="I27" t="str">
         <f t="shared" si="0"/>
         <v>'CPR03117'</v>
       </c>
-      <c r="F27" t="s">
-        <v>654</v>
-      </c>
-      <c r="G27" t="str">
+      <c r="J27" t="s">
+        <v>654</v>
+      </c>
+      <c r="K27" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Cha Cha Cha 22XU CP26 Mar Kodawari'</v>
       </c>
-      <c r="H27" t="s">
-        <v>654</v>
-      </c>
-      <c r="I27" t="s">
+      <c r="L27" t="s">
+        <v>654</v>
+      </c>
+      <c r="M27" t="s">
         <v>680</v>
       </c>
-      <c r="L27">
+      <c r="P27">
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A28" s="7" t="s">
+    <row r="28" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A28" s="7">
+        <v>27</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>580</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="C28" s="8" t="s">
         <v>581</v>
       </c>
-      <c r="E28" t="str">
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="I28" t="str">
         <f t="shared" si="0"/>
         <v>'CPR03119'</v>
       </c>
-      <c r="F28" t="s">
-        <v>654</v>
-      </c>
-      <c r="G28" t="str">
+      <c r="J28" t="s">
+        <v>654</v>
+      </c>
+      <c r="K28" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Cha Cha Cha 22XU  CP34 Mar Kodawari'</v>
       </c>
-      <c r="H28" t="s">
-        <v>654</v>
-      </c>
-      <c r="I28" t="s">
+      <c r="L28" t="s">
+        <v>654</v>
+      </c>
+      <c r="M28" t="s">
         <v>681</v>
       </c>
-      <c r="L28">
+      <c r="P28">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A29" s="7" t="s">
+    <row r="29" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A29" s="7">
+        <v>28</v>
+      </c>
+      <c r="B29" s="7" t="s">
         <v>597</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="C29" s="8" t="s">
         <v>598</v>
       </c>
-      <c r="E29" t="str">
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="I29" t="str">
         <f t="shared" si="0"/>
         <v>'CPR03123'</v>
       </c>
-      <c r="F29" t="s">
-        <v>654</v>
-      </c>
-      <c r="G29" t="str">
+      <c r="J29" t="s">
+        <v>654</v>
+      </c>
+      <c r="K29" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Premium Tarima Chep Banda 3b'</v>
       </c>
-      <c r="H29" t="s">
-        <v>654</v>
-      </c>
-      <c r="I29" t="s">
+      <c r="L29" t="s">
+        <v>654</v>
+      </c>
+      <c r="M29" t="s">
         <v>682</v>
       </c>
-      <c r="L29">
+      <c r="P29">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="s">
+    <row r="30" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A30" s="8">
+        <v>29</v>
+      </c>
+      <c r="B30" s="8" t="s">
         <v>638</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="C30" s="8" t="s">
         <v>639</v>
       </c>
-      <c r="E30" t="str">
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="I30" t="str">
         <f t="shared" si="0"/>
         <v>'CPR03124'</v>
       </c>
-      <c r="F30" t="s">
-        <v>654</v>
-      </c>
-      <c r="G30" t="str">
+      <c r="J30" t="s">
+        <v>654</v>
+      </c>
+      <c r="K30" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Cha Cha Cha 22XU CP27 Mar Kodawari'</v>
       </c>
-      <c r="H30" t="s">
-        <v>654</v>
-      </c>
-      <c r="I30" t="s">
+      <c r="L30" t="s">
+        <v>654</v>
+      </c>
+      <c r="M30" t="s">
         <v>683</v>
       </c>
-      <c r="L30">
+      <c r="P30">
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A31" s="7" t="s">
+    <row r="31" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A31" s="7">
+        <v>30</v>
+      </c>
+      <c r="B31" s="7" t="s">
         <v>607</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="C31" s="8" t="s">
         <v>608</v>
       </c>
-      <c r="E31" t="str">
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="I31" t="str">
         <f t="shared" si="0"/>
         <v>'CRG07125'</v>
       </c>
-      <c r="F31" t="s">
-        <v>654</v>
-      </c>
-      <c r="G31" t="str">
+      <c r="J31" t="s">
+        <v>654</v>
+      </c>
+      <c r="K31" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Organic Banded Tape Verde'</v>
       </c>
-      <c r="H31" t="s">
-        <v>654</v>
-      </c>
-      <c r="I31" t="s">
+      <c r="L31" t="s">
+        <v>654</v>
+      </c>
+      <c r="M31" t="s">
         <v>684</v>
       </c>
-      <c r="L31">
+      <c r="P31">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A32" s="7" t="s">
+    <row r="32" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A32" s="7">
+        <v>31</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>609</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="C32" s="8" t="s">
         <v>610</v>
       </c>
-      <c r="E32" t="str">
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="I32" t="str">
         <f t="shared" si="0"/>
         <v>'CRG07127'</v>
       </c>
-      <c r="F32" t="s">
-        <v>654</v>
-      </c>
-      <c r="G32" t="str">
+      <c r="J32" t="s">
+        <v>654</v>
+      </c>
+      <c r="K32" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Organic 3lb Banded Tape Morado'</v>
       </c>
-      <c r="H32" t="s">
-        <v>654</v>
-      </c>
-      <c r="I32" t="s">
+      <c r="L32" t="s">
+        <v>654</v>
+      </c>
+      <c r="M32" t="s">
         <v>685</v>
       </c>
-      <c r="L32">
+      <c r="P32">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A33" s="7" t="s">
+    <row r="33" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A33" s="7">
+        <v>32</v>
+      </c>
+      <c r="B33" s="7" t="s">
         <v>593</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="C33" s="8" t="s">
         <v>594</v>
       </c>
-      <c r="E33" t="str">
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="I33" t="str">
         <f t="shared" si="0"/>
         <v>'CRG07128'</v>
       </c>
-      <c r="F33" t="s">
-        <v>654</v>
-      </c>
-      <c r="G33" t="str">
+      <c r="J33" t="s">
+        <v>654</v>
+      </c>
+      <c r="K33" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Organic Banded Market Side Mexico'</v>
       </c>
-      <c r="H33" t="s">
-        <v>654</v>
-      </c>
-      <c r="I33" t="s">
+      <c r="L33" t="s">
+        <v>654</v>
+      </c>
+      <c r="M33" t="s">
         <v>686</v>
       </c>
-      <c r="L33">
+      <c r="P33">
         <f t="shared" si="2"/>
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A34" s="7" t="s">
+    <row r="34" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A34" s="7">
+        <v>33</v>
+      </c>
+      <c r="B34" s="7" t="s">
         <v>605</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="C34" s="8" t="s">
         <v>606</v>
       </c>
-      <c r="E34" t="str">
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="I34" t="str">
         <f t="shared" si="0"/>
         <v>'CRG07129'</v>
       </c>
-      <c r="F34" t="s">
-        <v>654</v>
-      </c>
-      <c r="G34" t="str">
+      <c r="J34" t="s">
+        <v>654</v>
+      </c>
+      <c r="K34" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Organic Banded Market Side EUA'</v>
       </c>
-      <c r="H34" t="s">
-        <v>654</v>
-      </c>
-      <c r="I34" t="s">
+      <c r="L34" t="s">
+        <v>654</v>
+      </c>
+      <c r="M34" t="s">
         <v>687</v>
       </c>
-      <c r="L34">
+      <c r="P34">
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
+    <row r="35" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A35" s="7">
+        <v>34</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>613</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="C35" s="8" t="s">
         <v>614</v>
       </c>
-      <c r="E35" t="str">
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="I35" t="str">
         <f t="shared" si="0"/>
         <v>'CRG07130'</v>
       </c>
-      <c r="F35" t="s">
-        <v>654</v>
-      </c>
-      <c r="G35" t="str">
+      <c r="J35" t="s">
+        <v>654</v>
+      </c>
+      <c r="K35" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Organic  22XU CP28 Union'</v>
       </c>
-      <c r="H35" t="s">
-        <v>654</v>
-      </c>
-      <c r="I35" t="s">
+      <c r="L35" t="s">
+        <v>654</v>
+      </c>
+      <c r="M35" t="s">
         <v>688</v>
       </c>
-      <c r="L35">
+      <c r="P35">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A36" s="7" t="s">
+    <row r="36" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A36" s="7">
+        <v>35</v>
+      </c>
+      <c r="B36" s="7" t="s">
         <v>611</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="C36" s="8" t="s">
         <v>612</v>
       </c>
-      <c r="E36" t="str">
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="I36" t="str">
         <f t="shared" si="0"/>
         <v>'CRG07131'</v>
       </c>
-      <c r="F36" t="s">
-        <v>654</v>
-      </c>
-      <c r="G36" t="str">
+      <c r="J36" t="s">
+        <v>654</v>
+      </c>
+      <c r="K36" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Organic  22XU CP34 Union'</v>
       </c>
-      <c r="H36" t="s">
-        <v>654</v>
-      </c>
-      <c r="I36" t="s">
+      <c r="L36" t="s">
+        <v>654</v>
+      </c>
+      <c r="M36" t="s">
         <v>689</v>
       </c>
-      <c r="L36">
+      <c r="P36">
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A37" s="7" t="s">
+    <row r="37" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A37" s="7">
+        <v>36</v>
+      </c>
+      <c r="B37" s="7" t="s">
         <v>626</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="C37" s="8" t="s">
         <v>629</v>
       </c>
-      <c r="E37" t="str">
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="I37" t="str">
         <f t="shared" si="0"/>
         <v>'CRG07132'</v>
       </c>
-      <c r="F37" t="s">
-        <v>654</v>
-      </c>
-      <c r="G37" t="str">
+      <c r="J37" t="s">
+        <v>654</v>
+      </c>
+      <c r="K37" t="str">
         <f t="shared" si="1"/>
         <v>'Organic  Wild Harvest '</v>
       </c>
-      <c r="H37" t="s">
-        <v>654</v>
-      </c>
-      <c r="I37" t="s">
+      <c r="L37" t="s">
+        <v>654</v>
+      </c>
+      <c r="M37" t="s">
         <v>690</v>
       </c>
-      <c r="L37">
+      <c r="P37">
         <f t="shared" si="2"/>
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A38" s="8" t="s">
+    <row r="38" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A38" s="8">
+        <v>37</v>
+      </c>
+      <c r="B38" s="8" t="s">
         <v>640</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="C38" s="8" t="s">
         <v>641</v>
       </c>
-      <c r="E38" t="str">
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="I38" t="str">
         <f t="shared" si="0"/>
         <v>'CRG07133'</v>
       </c>
-      <c r="F38" t="s">
-        <v>654</v>
-      </c>
-      <c r="G38" t="str">
+      <c r="J38" t="s">
+        <v>654</v>
+      </c>
+      <c r="K38" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Organic  Wild Harvest PLU94011'</v>
       </c>
-      <c r="H38" t="s">
-        <v>654</v>
-      </c>
-      <c r="I38" t="s">
+      <c r="L38" t="s">
+        <v>654</v>
+      </c>
+      <c r="M38" t="s">
         <v>691</v>
       </c>
-      <c r="L38">
+      <c r="P38">
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A39" s="7" t="s">
+    <row r="39" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A39" s="7">
+        <v>38</v>
+      </c>
+      <c r="B39" s="7" t="s">
         <v>587</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="C39" s="8" t="s">
         <v>588</v>
       </c>
-      <c r="E39" t="str">
+      <c r="D39">
+        <v>4</v>
+      </c>
+      <c r="I39" t="str">
         <f t="shared" si="0"/>
         <v>'CSA04120'</v>
       </c>
-      <c r="F39" t="s">
-        <v>654</v>
-      </c>
-      <c r="G39" t="str">
+      <c r="J39" t="s">
+        <v>654</v>
+      </c>
+      <c r="K39" t="str">
         <f t="shared" si="1"/>
         <v>'Chanitos Cha Cha Cha (2da) Granel'</v>
       </c>
-      <c r="H39" t="s">
-        <v>654</v>
-      </c>
-      <c r="I39" t="s">
+      <c r="L39" t="s">
+        <v>654</v>
+      </c>
+      <c r="M39" t="s">
         <v>692</v>
       </c>
-      <c r="L39">
+      <c r="P39">
         <f t="shared" si="2"/>
         <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B39" xr:uid="{961DD99E-A2C7-4E25-8FB0-84DFB4FA4937}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B39">
-      <sortCondition ref="A1:A39"/>
-    </sortState>
-  </autoFilter>
-  <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  <autoFilter ref="B1:D1" xr:uid="{961DD99E-A2C7-4E25-8FB0-84DFB4FA4937}"/>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A39">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -36209,7 +36458,7 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Datos.xlsx
+++ b/Datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chanitosfrutas-my.sharepoint.com/personal/bescobedo_chanitos_com/Documents/WorkSpace/preenfrio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="311" documentId="13_ncr:1_{F0A36C04-E6E5-4B51-9906-23526A19135B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E3B267F-3F95-4AD3-B07C-FE818ADA9922}"/>
+  <xr:revisionPtr revIDLastSave="312" documentId="13_ncr:1_{F0A36C04-E6E5-4B51-9906-23526A19135B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93BDAFDF-E20C-4591-9833-435D6350C2B7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{870F0A8F-B5CF-4FD7-9FD6-C646EB212759}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{870F0A8F-B5CF-4FD7-9FD6-C646EB212759}"/>
   </bookViews>
   <sheets>
     <sheet name="PREENFRIO" sheetId="1" r:id="rId1"/>
@@ -6241,7 +6241,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{329E6D9E-686A-4183-92BF-9B0AF16F6985}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:R284"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6300,7 +6299,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>131</v>
       </c>
@@ -6349,7 +6348,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>115</v>
       </c>
@@ -6399,7 +6398,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>106</v>
       </c>
@@ -6449,7 +6448,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>123</v>
       </c>
@@ -6499,7 +6498,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>534</v>
       </c>
@@ -6549,7 +6548,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>532</v>
       </c>
@@ -6599,7 +6598,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>557</v>
       </c>
@@ -6649,7 +6648,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>117</v>
       </c>
@@ -6699,7 +6698,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>98</v>
       </c>
@@ -6749,7 +6748,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>146</v>
       </c>
@@ -6799,7 +6798,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>144</v>
       </c>
@@ -6849,7 +6848,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>127</v>
       </c>
@@ -6899,7 +6898,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>479</v>
       </c>
@@ -6949,7 +6948,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>137</v>
       </c>
@@ -6999,7 +6998,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>139</v>
       </c>
@@ -7049,7 +7048,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>141</v>
       </c>
@@ -7099,7 +7098,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>110</v>
       </c>
@@ -7149,7 +7148,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>475</v>
       </c>
@@ -7199,7 +7198,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>481</v>
       </c>
@@ -7249,7 +7248,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>516</v>
       </c>
@@ -7299,7 +7298,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>559</v>
       </c>
@@ -7349,7 +7348,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>133</v>
       </c>
@@ -7399,7 +7398,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>142</v>
       </c>
@@ -7449,7 +7448,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>96</v>
       </c>
@@ -7499,7 +7498,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>100</v>
       </c>
@@ -7549,7 +7548,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>555</v>
       </c>
@@ -7599,7 +7598,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>418</v>
       </c>
@@ -7649,7 +7648,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>104</v>
       </c>
@@ -7699,7 +7698,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>148</v>
       </c>
@@ -7749,7 +7748,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>102</v>
       </c>
@@ -7799,7 +7798,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>108</v>
       </c>
@@ -7849,7 +7848,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>530</v>
       </c>
@@ -7899,7 +7898,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>135</v>
       </c>
@@ -7949,7 +7948,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>129</v>
       </c>
@@ -7999,7 +7998,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>121</v>
       </c>
@@ -8049,7 +8048,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>119</v>
       </c>
@@ -8099,7 +8098,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>125</v>
       </c>
@@ -8149,7 +8148,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>114</v>
       </c>
@@ -8199,7 +8198,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>112</v>
       </c>
@@ -8249,7 +8248,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>477</v>
       </c>
@@ -8299,7 +8298,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>536</v>
       </c>
@@ -8349,7 +8348,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
         <v>392</v>
       </c>
@@ -8399,7 +8398,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>198</v>
       </c>
@@ -8449,7 +8448,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
         <v>163</v>
       </c>
@@ -8499,7 +8498,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>261</v>
       </c>
@@ -8549,7 +8548,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>153</v>
       </c>
@@ -8599,7 +8598,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>430</v>
       </c>
@@ -8649,7 +8648,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>170</v>
       </c>
@@ -8699,7 +8698,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>368</v>
       </c>
@@ -8749,7 +8748,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
         <v>565</v>
       </c>
@@ -8799,7 +8798,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>308</v>
       </c>
@@ -8849,7 +8848,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
         <v>400</v>
       </c>
@@ -8899,7 +8898,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
         <v>226</v>
       </c>
@@ -8949,7 +8948,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>225</v>
       </c>
@@ -8999,7 +8998,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
         <v>328</v>
       </c>
@@ -9049,7 +9048,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
         <v>432</v>
       </c>
@@ -9099,7 +9098,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
         <v>188</v>
       </c>
@@ -9149,7 +9148,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
         <v>561</v>
       </c>
@@ -9199,7 +9198,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
         <v>189</v>
       </c>
@@ -9249,7 +9248,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
         <v>343</v>
       </c>
@@ -9299,7 +9298,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
         <v>318</v>
       </c>
@@ -9349,7 +9348,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>330</v>
       </c>
@@ -9399,7 +9398,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>168</v>
       </c>
@@ -9449,7 +9448,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
         <v>172</v>
       </c>
@@ -9499,7 +9498,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
         <v>242</v>
       </c>
@@ -9549,7 +9548,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
         <v>287</v>
       </c>
@@ -9599,7 +9598,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
         <v>366</v>
       </c>
@@ -9649,7 +9648,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
         <v>567</v>
       </c>
@@ -9699,7 +9698,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
         <v>233</v>
       </c>
@@ -9749,7 +9748,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
         <v>484</v>
       </c>
@@ -9799,7 +9798,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
         <v>251</v>
       </c>
@@ -9849,7 +9848,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
         <v>391</v>
       </c>
@@ -9899,7 +9898,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
         <v>553</v>
       </c>
@@ -9949,7 +9948,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
         <v>150</v>
       </c>
@@ -9999,7 +9998,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
         <v>196</v>
       </c>
@@ -10049,7 +10048,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
         <v>364</v>
       </c>
@@ -10099,7 +10098,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="78" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
         <v>365</v>
       </c>
@@ -10149,7 +10148,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
         <v>398</v>
       </c>
@@ -10199,7 +10198,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
         <v>538</v>
       </c>
@@ -10249,7 +10248,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
         <v>267</v>
       </c>
@@ -10299,7 +10298,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
         <v>200</v>
       </c>
@@ -10349,7 +10348,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
         <v>346</v>
       </c>
@@ -10399,7 +10398,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
         <v>352</v>
       </c>
@@ -10449,7 +10448,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
         <v>355</v>
       </c>
@@ -10499,7 +10498,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
         <v>212</v>
       </c>
@@ -10549,7 +10548,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
         <v>442</v>
       </c>
@@ -10599,7 +10598,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
         <v>449</v>
       </c>
@@ -10649,7 +10648,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
         <v>275</v>
       </c>
@@ -10699,7 +10698,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
         <v>349</v>
       </c>
@@ -10749,7 +10748,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
         <v>273</v>
       </c>
@@ -10799,7 +10798,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
         <v>428</v>
       </c>
@@ -10849,7 +10848,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A93" s="6" t="s">
         <v>177</v>
       </c>
@@ -10899,7 +10898,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A94" s="6" t="s">
         <v>205</v>
       </c>
@@ -10949,7 +10948,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="s">
         <v>446</v>
       </c>
@@ -10999,7 +10998,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A96" s="6" t="s">
         <v>486</v>
       </c>
@@ -11049,7 +11048,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
         <v>455</v>
       </c>
@@ -11099,7 +11098,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
         <v>310</v>
       </c>
@@ -11149,7 +11148,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A99" s="6" t="s">
         <v>537</v>
       </c>
@@ -11199,7 +11198,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
         <v>407</v>
       </c>
@@ -11249,7 +11248,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
         <v>203</v>
       </c>
@@ -11299,7 +11298,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="s">
         <v>219</v>
       </c>
@@ -11349,7 +11348,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A103" s="6" t="s">
         <v>437</v>
       </c>
@@ -11399,7 +11398,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
         <v>509</v>
       </c>
@@ -11449,7 +11448,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A105" s="6" t="s">
         <v>238</v>
       </c>
@@ -11499,7 +11498,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A106" s="6" t="s">
         <v>569</v>
       </c>
@@ -11549,7 +11548,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A107" s="6" t="s">
         <v>320</v>
       </c>
@@ -11599,7 +11598,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A108" s="6" t="s">
         <v>572</v>
       </c>
@@ -11649,7 +11648,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A109" s="6" t="s">
         <v>340</v>
       </c>
@@ -11699,7 +11698,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A110" s="6" t="s">
         <v>295</v>
       </c>
@@ -11749,7 +11748,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A111" s="6" t="s">
         <v>459</v>
       </c>
@@ -11799,7 +11798,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A112" s="6" t="s">
         <v>290</v>
       </c>
@@ -11849,7 +11848,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A113" s="6" t="s">
         <v>305</v>
       </c>
@@ -11899,7 +11898,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A114" s="6" t="s">
         <v>324</v>
       </c>
@@ -11949,7 +11948,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A115" s="6" t="s">
         <v>271</v>
       </c>
@@ -11999,7 +11998,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A116" s="6" t="s">
         <v>316</v>
       </c>
@@ -12049,7 +12048,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A117" s="6" t="s">
         <v>374</v>
       </c>
@@ -12099,7 +12098,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A118" s="6" t="s">
         <v>376</v>
       </c>
@@ -12149,7 +12148,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A119" s="6" t="s">
         <v>436</v>
       </c>
@@ -12199,7 +12198,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A120" s="6" t="s">
         <v>217</v>
       </c>
@@ -12249,7 +12248,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A121" s="6" t="s">
         <v>307</v>
       </c>
@@ -12299,7 +12298,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="122" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A122" s="6" t="s">
         <v>568</v>
       </c>
@@ -12349,7 +12348,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A123" s="6" t="s">
         <v>506</v>
       </c>
@@ -12399,7 +12398,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="124" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A124" s="6" t="s">
         <v>231</v>
       </c>
@@ -12449,7 +12448,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="125" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A125" s="6" t="s">
         <v>159</v>
       </c>
@@ -12499,7 +12498,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A126" s="6" t="s">
         <v>548</v>
       </c>
@@ -12549,7 +12548,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A127" s="6" t="s">
         <v>161</v>
       </c>
@@ -12599,7 +12598,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A128" s="6" t="s">
         <v>422</v>
       </c>
@@ -12649,7 +12648,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A129" s="6" t="s">
         <v>491</v>
       </c>
@@ -12699,7 +12698,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A130" s="6" t="s">
         <v>494</v>
       </c>
@@ -12749,7 +12748,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A131" s="6" t="s">
         <v>298</v>
       </c>
@@ -12799,7 +12798,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A132" s="6" t="s">
         <v>288</v>
       </c>
@@ -12849,7 +12848,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A133" s="6" t="s">
         <v>405</v>
       </c>
@@ -12899,7 +12898,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A134" s="6" t="s">
         <v>383</v>
       </c>
@@ -12949,7 +12948,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A135" s="6" t="s">
         <v>245</v>
       </c>
@@ -12999,7 +12998,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A136" s="6" t="s">
         <v>372</v>
       </c>
@@ -13049,7 +13048,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A137" s="6" t="s">
         <v>502</v>
       </c>
@@ -13099,7 +13098,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A138" s="6" t="s">
         <v>541</v>
       </c>
@@ -13149,7 +13148,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A139" s="6" t="s">
         <v>381</v>
       </c>
@@ -13199,7 +13198,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A140" s="6" t="s">
         <v>247</v>
       </c>
@@ -13249,7 +13248,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A141" s="6" t="s">
         <v>439</v>
       </c>
@@ -13299,7 +13298,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A142" s="6" t="s">
         <v>357</v>
       </c>
@@ -13349,7 +13348,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A143" s="6" t="s">
         <v>157</v>
       </c>
@@ -13399,7 +13398,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A144" s="6" t="s">
         <v>332</v>
       </c>
@@ -13449,7 +13448,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="145" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A145" s="6" t="s">
         <v>279</v>
       </c>
@@ -13499,7 +13498,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="146" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A146" s="6" t="s">
         <v>263</v>
       </c>
@@ -13549,7 +13548,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="147" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A147" s="6" t="s">
         <v>496</v>
       </c>
@@ -13599,7 +13598,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="148" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A148" s="6" t="s">
         <v>249</v>
       </c>
@@ -13649,7 +13648,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="149" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A149" s="6" t="s">
         <v>379</v>
       </c>
@@ -13699,7 +13698,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="150" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A150" s="6" t="s">
         <v>377</v>
       </c>
@@ -13749,7 +13748,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="151" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A151" s="6" t="s">
         <v>370</v>
       </c>
@@ -13799,7 +13798,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="152" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A152" s="6" t="s">
         <v>155</v>
       </c>
@@ -14599,7 +14598,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="168" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A168" s="6" t="s">
         <v>394</v>
       </c>
@@ -14649,7 +14648,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A169" s="6" t="s">
         <v>444</v>
       </c>
@@ -14699,7 +14698,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="170" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A170" s="6" t="s">
         <v>326</v>
       </c>
@@ -14749,7 +14748,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="171" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A171" s="6" t="s">
         <v>359</v>
       </c>
@@ -14799,7 +14798,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="172" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A172" s="6" t="s">
         <v>302</v>
       </c>
@@ -14849,7 +14848,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="173" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A173" s="6" t="s">
         <v>519</v>
       </c>
@@ -14899,7 +14898,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="174" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A174" s="6" t="s">
         <v>322</v>
       </c>
@@ -14949,7 +14948,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="175" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A175" s="6" t="s">
         <v>411</v>
       </c>
@@ -14999,7 +14998,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="176" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A176" s="6" t="s">
         <v>296</v>
       </c>
@@ -15049,7 +15048,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="177" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A177" s="6" t="s">
         <v>214</v>
       </c>
@@ -15099,7 +15098,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="178" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A178" s="6" t="s">
         <v>216</v>
       </c>
@@ -15149,7 +15148,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="179" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A179" s="6" t="s">
         <v>483</v>
       </c>
@@ -15199,7 +15198,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="180" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A180" s="6" t="s">
         <v>210</v>
       </c>
@@ -15249,7 +15248,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="181" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A181" s="6" t="s">
         <v>363</v>
       </c>
@@ -15299,7 +15298,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="182" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A182" s="6" t="s">
         <v>453</v>
       </c>
@@ -15349,7 +15348,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="183" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A183" s="6" t="s">
         <v>253</v>
       </c>
@@ -15399,7 +15398,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="184" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A184" s="6" t="s">
         <v>414</v>
       </c>
@@ -15449,7 +15448,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="185" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A185" s="6" t="s">
         <v>283</v>
       </c>
@@ -15499,7 +15498,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="186" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A186" s="6" t="s">
         <v>221</v>
       </c>
@@ -15549,7 +15548,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="187" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A187" s="6" t="s">
         <v>424</v>
       </c>
@@ -15599,7 +15598,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="188" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A188" s="6" t="s">
         <v>181</v>
       </c>
@@ -15649,7 +15648,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="189" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A189" s="6" t="s">
         <v>426</v>
       </c>
@@ -15699,7 +15698,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="190" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A190" s="6" t="s">
         <v>416</v>
       </c>
@@ -15749,7 +15748,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="191" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A191" s="6" t="s">
         <v>194</v>
       </c>
@@ -15799,7 +15798,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="192" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A192" s="6" t="s">
         <v>312</v>
       </c>
@@ -15849,7 +15848,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="193" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A193" s="6" t="s">
         <v>183</v>
       </c>
@@ -15899,7 +15898,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="194" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A194" s="6" t="s">
         <v>185</v>
       </c>
@@ -15949,7 +15948,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="195" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A195" s="6" t="s">
         <v>336</v>
       </c>
@@ -15999,7 +15998,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="196" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A196" s="6" t="s">
         <v>281</v>
       </c>
@@ -16049,7 +16048,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="197" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A197" s="6" t="s">
         <v>338</v>
       </c>
@@ -16099,7 +16098,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="198" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A198" s="6" t="s">
         <v>334</v>
       </c>
@@ -16149,7 +16148,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A199" s="6" t="s">
         <v>434</v>
       </c>
@@ -16199,7 +16198,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A200" s="6" t="s">
         <v>419</v>
       </c>
@@ -16249,7 +16248,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="201" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A201" s="6" t="s">
         <v>513</v>
       </c>
@@ -16299,7 +16298,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="202" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A202" s="6" t="s">
         <v>269</v>
       </c>
@@ -16349,7 +16348,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="203" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A203" s="6" t="s">
         <v>462</v>
       </c>
@@ -16399,7 +16398,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="204" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A204" s="6" t="s">
         <v>174</v>
       </c>
@@ -16449,7 +16448,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="205" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A205" s="6" t="s">
         <v>385</v>
       </c>
@@ -16499,7 +16498,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="206" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A206" s="6" t="s">
         <v>460</v>
       </c>
@@ -16549,7 +16548,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="207" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A207" s="6" t="s">
         <v>176</v>
       </c>
@@ -16599,7 +16598,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="208" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A208" s="6" t="s">
         <v>539</v>
       </c>
@@ -16649,7 +16648,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="209" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A209" s="6" t="s">
         <v>653</v>
       </c>
@@ -16699,7 +16698,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="210" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A210" s="6" t="s">
         <v>165</v>
       </c>
@@ -16749,7 +16748,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="211" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A211" s="6" t="s">
         <v>311</v>
       </c>
@@ -16799,7 +16798,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="212" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A212" s="6" t="s">
         <v>348</v>
       </c>
@@ -16849,7 +16848,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="213" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A213" s="6" t="s">
         <v>285</v>
       </c>
@@ -16899,7 +16898,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="214" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A214" s="6" t="s">
         <v>228</v>
       </c>
@@ -16949,7 +16948,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="215" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A215" s="6" t="s">
         <v>493</v>
       </c>
@@ -16999,7 +16998,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="216" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A216" s="6" t="s">
         <v>230</v>
       </c>
@@ -17049,7 +17048,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="217" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A217" s="6" t="s">
         <v>227</v>
       </c>
@@ -17099,7 +17098,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="218" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A218" s="6" t="s">
         <v>223</v>
       </c>
@@ -17149,7 +17148,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="219" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A219" s="6" t="s">
         <v>229</v>
       </c>
@@ -17199,7 +17198,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="220" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A220" s="6" t="s">
         <v>341</v>
       </c>
@@ -17249,7 +17248,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="221" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A221" s="6" t="s">
         <v>292</v>
       </c>
@@ -17299,7 +17298,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="222" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A222" s="6" t="s">
         <v>294</v>
       </c>
@@ -17349,7 +17348,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="223" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A223" s="6" t="s">
         <v>457</v>
       </c>
@@ -17399,7 +17398,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="224" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A224" s="6" t="s">
         <v>300</v>
       </c>
@@ -17449,7 +17448,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="225" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A225" s="6" t="s">
         <v>240</v>
       </c>
@@ -17499,7 +17498,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="226" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A226" s="6" t="s">
         <v>518</v>
       </c>
@@ -17549,7 +17548,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="227" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A227" s="6" t="s">
         <v>409</v>
       </c>
@@ -17599,7 +17598,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="228" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A228" s="6" t="s">
         <v>235</v>
       </c>
@@ -17649,7 +17648,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="229" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A229" s="6" t="s">
         <v>539</v>
       </c>
@@ -17699,7 +17698,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="230" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A230" s="6" t="s">
         <v>243</v>
       </c>
@@ -17749,7 +17748,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="231" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A231" s="6" t="s">
         <v>265</v>
       </c>
@@ -17799,7 +17798,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="232" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A232" s="6" t="s">
         <v>540</v>
       </c>
@@ -17849,7 +17848,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="233" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A233" s="6" t="s">
         <v>152</v>
       </c>
@@ -17899,7 +17898,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="234" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A234" s="6" t="s">
         <v>387</v>
       </c>
@@ -17949,7 +17948,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="235" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A235" s="6" t="s">
         <v>344</v>
       </c>
@@ -17999,7 +17998,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="236" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A236" s="6" t="s">
         <v>361</v>
       </c>
@@ -18049,7 +18048,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="237" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A237" s="6" t="s">
         <v>402</v>
       </c>
@@ -18099,7 +18098,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="238" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A238" s="6" t="s">
         <v>404</v>
       </c>
@@ -18149,7 +18148,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="239" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A239" s="6" t="s">
         <v>314</v>
       </c>
@@ -18199,7 +18198,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="240" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A240" s="6" t="s">
         <v>255</v>
       </c>
@@ -18249,7 +18248,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="241" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A241" s="6" t="s">
         <v>396</v>
       </c>
@@ -18299,7 +18298,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="242" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A242" s="6" t="s">
         <v>191</v>
       </c>
@@ -18349,7 +18348,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="243" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A243" s="6" t="s">
         <v>179</v>
       </c>
@@ -18399,7 +18398,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="244" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A244" s="6" t="s">
         <v>236</v>
       </c>
@@ -18449,7 +18448,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="245" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A245" s="6" t="s">
         <v>208</v>
       </c>
@@ -18499,7 +18498,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="246" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A246" s="6" t="s">
         <v>166</v>
       </c>
@@ -18549,7 +18548,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="247" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A247" s="6" t="s">
         <v>500</v>
       </c>
@@ -18599,7 +18598,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="248" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A248" s="6" t="s">
         <v>545</v>
       </c>
@@ -18649,7 +18648,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="249" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A249" s="6" t="s">
         <v>546</v>
       </c>
@@ -18699,7 +18698,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="250" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A250" s="6" t="s">
         <v>202</v>
       </c>
@@ -18749,7 +18748,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="251" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A251" s="6" t="s">
         <v>499</v>
       </c>
@@ -18799,7 +18798,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="252" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A252" s="6" t="s">
         <v>489</v>
       </c>
@@ -18849,7 +18848,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="253" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A253" s="6" t="s">
         <v>490</v>
       </c>
@@ -18899,7 +18898,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="254" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A254" s="6" t="s">
         <v>354</v>
       </c>
@@ -18949,7 +18948,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="255" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A255" s="6" t="s">
         <v>448</v>
       </c>
@@ -18999,7 +18998,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="256" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A256" s="6" t="s">
         <v>447</v>
       </c>
@@ -19049,7 +19048,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="257" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A257" s="6" t="s">
         <v>452</v>
       </c>
@@ -19099,7 +19098,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="258" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A258" s="6" t="s">
         <v>451</v>
       </c>
@@ -19149,7 +19148,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="259" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A259" s="6" t="s">
         <v>277</v>
       </c>
@@ -19199,7 +19198,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="260" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A260" s="6" t="s">
         <v>278</v>
       </c>
@@ -19249,7 +19248,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="261" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A261" s="6" t="s">
         <v>351</v>
       </c>
@@ -19299,7 +19298,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="262" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A262" s="6" t="s">
         <v>207</v>
       </c>
@@ -19349,7 +19348,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="263" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A263" s="6" t="s">
         <v>564</v>
       </c>
@@ -19399,7 +19398,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="264" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A264" s="6" t="s">
         <v>511</v>
       </c>
@@ -19449,7 +19448,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="265" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A265" s="6" t="s">
         <v>549</v>
       </c>
@@ -19499,7 +19498,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="266" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A266" s="6" t="s">
         <v>445</v>
       </c>
@@ -19549,7 +19548,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="267" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A267" s="6" t="s">
         <v>193</v>
       </c>
@@ -19599,7 +19598,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="268" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A268" s="6" t="s">
         <v>508</v>
       </c>
@@ -19649,7 +19648,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="269" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A269" s="6" t="s">
         <v>488</v>
       </c>
@@ -19699,7 +19698,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="270" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A270" s="6" t="s">
         <v>469</v>
       </c>
@@ -19749,7 +19748,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="271" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A271" s="6" t="s">
         <v>471</v>
       </c>
@@ -19799,7 +19798,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="272" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A272" s="6" t="s">
         <v>526</v>
       </c>
@@ -19849,7 +19848,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="273" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A273" s="6" t="s">
         <v>463</v>
       </c>
@@ -19899,7 +19898,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="274" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A274" s="6" t="s">
         <v>473</v>
       </c>
@@ -19949,7 +19948,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="275" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A275" s="6" t="s">
         <v>543</v>
       </c>
@@ -19999,7 +19998,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="276" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A276" s="6" t="s">
         <v>528</v>
       </c>
@@ -20049,7 +20048,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="277" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A277" s="6" t="s">
         <v>497</v>
       </c>
@@ -20099,7 +20098,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="278" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A278" s="6" t="s">
         <v>465</v>
       </c>
@@ -20149,7 +20148,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="279" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A279" s="6" t="s">
         <v>522</v>
       </c>
@@ -20199,7 +20198,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="280" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A280" s="6" t="s">
         <v>520</v>
       </c>
@@ -20249,7 +20248,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="281" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A281" s="6" t="s">
         <v>571</v>
       </c>
@@ -20299,7 +20298,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="282" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A282" s="6" t="s">
         <v>467</v>
       </c>
@@ -20349,7 +20348,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="283" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A283" s="6" t="s">
         <v>524</v>
       </c>
@@ -20399,7 +20398,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="284" spans="1:18" ht="22.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A284" s="6" t="s">
         <v>514</v>
       </c>
@@ -20484,13 +20483,7 @@
     <protectedRange algorithmName="SHA-512" hashValue="oAofLzPsEABz+g8s4EYjUuwXH7ykbMbBHfCBkrjaG9AypkvLlHymmath48lOXQru/nByDYQVi/KXn1fge9PtNA==" saltValue="K19iw11Oiq05wm1mPIKVDQ==" spinCount="100000" sqref="D276" name="Rango4_30"/>
     <protectedRange algorithmName="SHA-512" hashValue="oAofLzPsEABz+g8s4EYjUuwXH7ykbMbBHfCBkrjaG9AypkvLlHymmath48lOXQru/nByDYQVi/KXn1fge9PtNA==" saltValue="K19iw11Oiq05wm1mPIKVDQ==" spinCount="100000" sqref="D277" name="Rango4_31"/>
   </protectedRanges>
-  <autoFilter ref="A1:O284" xr:uid="{329E6D9E-686A-4183-92BF-9B0AF16F6985}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="124"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:O284" xr:uid="{329E6D9E-686A-4183-92BF-9B0AF16F6985}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -21849,11 +21842,11 @@
     </row>
   </sheetData>
   <autoFilter ref="B1:D1" xr:uid="{961DD99E-A2C7-4E25-8FB0-84DFB4FA4937}"/>
+  <conditionalFormatting sqref="A1:A39">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A39">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -36458,7 +36451,7 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
